--- a/naver-place-crawler/results_health/원주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/원주_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4134</v>
+        <v>4136</v>
       </c>
       <c r="Q2" t="n">
         <v>814</v>
       </c>
       <c r="R2" t="n">
-        <v>4948</v>
+        <v>4950</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바디라인휘트니스 원주무실점</t>
+          <t>무실동 듀플릿 헬스\u002FPT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bodyline2@naver.com</t>
+          <t>jin10240107@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1428-3415</t>
+          <t>0507-1306-6059</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 48-1 5층</t>
+          <t>강원 원주시 능라동길 70 5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline2</t>
+          <t>https://blog.naver.com/jin10240107</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4loqz</t>
+          <t>https://talk.naver.com/ct/w4b6cm</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>706</v>
+        <v>3475</v>
       </c>
       <c r="Q3" t="n">
-        <v>703</v>
+        <v>736</v>
       </c>
       <c r="R3" t="n">
-        <v>1409</v>
+        <v>4211</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1140023595</t>
+          <t>1659772512</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140023595</t>
+          <t>https://m.place.naver.com/place/1659772512</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>무실동 듀플릿 헬스\u002FPT</t>
+          <t>바디라인휘트니스 원주무실점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jin10240107@naver.com</t>
+          <t>bodyline2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1306-6059</t>
+          <t>0507-1428-3415</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 70 5층</t>
+          <t>강원 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jin10240107</t>
+          <t>https://blog.naver.com/bodyline2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4b6cm</t>
+          <t>https://talk.naver.com/ct/w4loqz</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3475</v>
+        <v>707</v>
       </c>
       <c r="Q4" t="n">
-        <v>736</v>
+        <v>704</v>
       </c>
       <c r="R4" t="n">
-        <v>4211</v>
+        <v>1411</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1659772512</t>
+          <t>1140023595</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659772512</t>
+          <t>https://m.place.naver.com/place/1140023595</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mega_gym_pilates@naver.com</t>
+          <t>megagym9932@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mega_gym_pilates</t>
+          <t>https://blog.naver.com/megagym9932</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="Q5" t="n">
         <v>332</v>
       </c>
       <c r="R5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>374</v>
       </c>
       <c r="Q6" t="n">
-        <v>2132</v>
+        <v>2136</v>
       </c>
       <c r="R6" t="n">
-        <v>2506</v>
+        <v>2510</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>taiwansister@naver.com</t>
+          <t>crossfitturtle@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1233,34 +1233,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비플로우PT&amp;그룹PT</t>
+          <t>엠투짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bflowpt@naver.com</t>
+          <t>k1140391@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1437-1576</t>
+          <t>0507-1358-1467</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 9 3층 비플로우</t>
+          <t>강원 원주시 혁신로 39-2 서울메디컬센터 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bflowpt</t>
+          <t>https://www.instagram.com/m2gym.spinning</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h9q7</t>
+          <t>https://talk.naver.com/ct/wtjdyz5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="Q9" t="n">
-        <v>660</v>
+        <v>29</v>
       </c>
       <c r="R9" t="n">
-        <v>893</v>
+        <v>204</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1870827414</t>
+          <t>37912788</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870827414</t>
+          <t>https://m.place.naver.com/place/37912788</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,29 +1336,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>혁신런앤핏</t>
+          <t>비플로우PT&amp;그룹PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hghghghg00@naver.com</t>
+          <t>bflowpt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1346-7262</t>
+          <t>0507-1437-1576</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>강원 원주시 혁신로 19 지하층 101호</t>
+          <t>강원 원주시 능라동길 9 3층 비플로우</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hs_run_fit</t>
+          <t>https://blog.naver.com/bflowpt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,15 +1373,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h9q7</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1393,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>660</v>
       </c>
       <c r="R10" t="n">
-        <v>22</v>
+        <v>893</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1223719800</t>
+          <t>1870827414</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223719800</t>
+          <t>https://m.place.naver.com/place/1870827414</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/원주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/원주_헬스장.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>호크아이짐 헬스\u002FPT\u002F태닝</t>
+          <t>무실동 듀플릿 헬스\u002FPT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hawkeyegym@naver.com</t>
+          <t>jin10240107@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1307-5822</t>
+          <t>0507-1306-6059</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 원주시 서원대로 106 3층 호크아이짐</t>
+          <t>강원 원주시 능라동길 70 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hawkeyegym</t>
+          <t>https://blog.naver.com/jin10240107</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cqnu</t>
+          <t>https://talk.naver.com/ct/w4b6cm</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4136</v>
+        <v>3493</v>
       </c>
       <c r="Q2" t="n">
-        <v>814</v>
+        <v>740</v>
       </c>
       <c r="R2" t="n">
-        <v>4950</v>
+        <v>4233</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1602901180</t>
+          <t>1659772512</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1602901180</t>
+          <t>https://m.place.naver.com/place/1659772512</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>무실동 듀플릿 헬스\u002FPT</t>
+          <t>호크아이짐 헬스\u002FPT\u002F태닝</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jin10240107@naver.com</t>
+          <t>hawkeyegym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1306-6059</t>
+          <t>0507-1307-5822</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 70 5층</t>
+          <t>강원 원주시 서원대로 106 3층 호크아이짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jin10240107</t>
+          <t>https://blog.naver.com/hawkeyegym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4b6cm</t>
+          <t>https://talk.naver.com/ct/w4cqnu</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3475</v>
+        <v>4184</v>
       </c>
       <c r="Q3" t="n">
-        <v>736</v>
+        <v>814</v>
       </c>
       <c r="R3" t="n">
-        <v>4211</v>
+        <v>4998</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1659772512</t>
+          <t>1602901180</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659772512</t>
+          <t>https://m.place.naver.com/place/1602901180</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바디라인휘트니스 원주무실점</t>
+          <t>24시 피트니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bodyline2@naver.com</t>
+          <t>24hourfitness_@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1428-3415</t>
+          <t>033-766-4048</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 48-1 5층</t>
+          <t>강원 원주시 서원대로 474 1, 2층 24시피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline2</t>
+          <t>https://www.instagram.com/24hoursfitness2020/?hl=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4loqz</t>
+          <t>https://talk.naver.com/ct/w4jwb5</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>707</v>
+        <v>894</v>
       </c>
       <c r="Q4" t="n">
-        <v>704</v>
+        <v>127</v>
       </c>
       <c r="R4" t="n">
-        <v>1411</v>
+        <v>1021</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1140023595</t>
+          <t>1016379546</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140023595</t>
+          <t>https://m.place.naver.com/place/1016379546</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>메가짐 PT&amp;필라테스</t>
+          <t>바디라인휘트니스 원주무실점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>megagym9932@naver.com</t>
+          <t>bodyline2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1325-9932</t>
+          <t>0507-1428-3415</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 원주시 서원대로 165-3 아트스페이스 5층</t>
+          <t>강원 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/megagym9932</t>
+          <t>https://blog.naver.com/bodyline2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tavv</t>
+          <t>https://talk.naver.com/ct/w4loqz</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1682</v>
+        <v>714</v>
       </c>
       <c r="Q5" t="n">
-        <v>332</v>
+        <v>723</v>
       </c>
       <c r="R5" t="n">
-        <v>2014</v>
+        <v>1437</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,51 +934,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1302676152</t>
+          <t>1140023595</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302676152</t>
+          <t>https://m.place.naver.com/place/1140023595</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>비브레 PT\u002F헬스 혁신점</t>
+          <t>메가짐 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wonju_ht@naver.com</t>
+          <t>megagym9932@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1354-8955</t>
+          <t>0507-1325-9932</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원 원주시 서원대로 165-3 아트스페이스 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://vivre-training.com/</t>
+          <t>https://blog.naver.com/megagym9932</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46eja</t>
+          <t>https://talk.naver.com/ct/w5tavv</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>374</v>
+        <v>1716</v>
       </c>
       <c r="Q6" t="n">
-        <v>2136</v>
+        <v>336</v>
       </c>
       <c r="R6" t="n">
-        <v>2510</v>
+        <v>2052</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1193233179</t>
+          <t>1302676152</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193233179</t>
+          <t>https://m.place.naver.com/place/1302676152</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,25 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>크로스핏 컴뱃</t>
+          <t>팀키스짐 &amp; PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>crossfitturtle@naver.com</t>
+          <t>teamkis_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1399-2305</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 원주시 만대공원길 64 1층</t>
+          <t>강원 원주시 능라동길 26 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit__combat</t>
+          <t>https://blog.naver.com/teamkis_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,15 +1091,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4olwd</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1107,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>166</v>
+        <v>2319</v>
       </c>
       <c r="Q7" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="R7" t="n">
-        <v>210</v>
+        <v>2819</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36369149</t>
+          <t>1433616376</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36369149</t>
+          <t>https://m.place.naver.com/place/1433616376</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1152,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>하이컴뱃</t>
+          <t>크로스핏 컴뱃</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1153,20 +1161,16 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1347-5120</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 송삼길 19 1층</t>
+          <t>강원 원주시 만대공원길 64 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hycombat__</t>
+          <t>https://www.instagram.com/crossfit__combat</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1201,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>166</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="R8" t="n">
-        <v>37</v>
+        <v>210</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,51 +1220,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2058886633</t>
+          <t>36369149</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058886633</t>
+          <t>https://m.place.naver.com/place/36369149</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엠투짐</t>
+          <t>비브레 PT\u002F헬스 혁신점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>k1140391@naver.com</t>
+          <t>wonju_ht@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1358-1467</t>
+          <t>0507-1354-8955</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 혁신로 39-2 서울메디컬센터 5층</t>
+          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/m2gym.spinning</t>
+          <t>http://vivre-training.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wtjdyz5</t>
+          <t>https://talk.naver.com/ct/w46eja</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>175</v>
+        <v>378</v>
       </c>
       <c r="Q9" t="n">
-        <v>29</v>
+        <v>2174</v>
       </c>
       <c r="R9" t="n">
-        <v>204</v>
+        <v>2552</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37912788</t>
+          <t>1193233179</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37912788</t>
+          <t>https://m.place.naver.com/place/1193233179</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1397,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q10" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="R10" t="n">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/원주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/원주_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>무실동 듀플릿 헬스\u002FPT</t>
+          <t>에이스스포츠센터&amp;에이스짐PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jin10240107@naver.com</t>
+          <t>jth3824@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1306-6059</t>
+          <t>0507-1336-5769</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 70 5층</t>
+          <t>강원특별자치도 원주시 원일로115번길 16 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jin10240107</t>
+          <t>https://www.instagram.com/acegym_wonju</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4b6cm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3493</v>
+        <v>1583</v>
       </c>
       <c r="Q2" t="n">
-        <v>740</v>
+        <v>919</v>
       </c>
       <c r="R2" t="n">
-        <v>4233</v>
+        <v>2502</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1659772512</t>
+          <t>15201329</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659772512</t>
+          <t>https://m.place.naver.com/place/15201329</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>호크아이짐 헬스\u002FPT\u002F태닝</t>
+          <t>크로스핏BnK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hawkeyegym@naver.com</t>
+          <t>dldbsrnjs11@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1307-5822</t>
+          <t>0507-1359-0221</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 원주시 서원대로 106 3층 호크아이짐</t>
+          <t>강원특별자치도 원주시 나비허리길 97 2동 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hawkeyegym</t>
+          <t>https://www.instagram.com/crossfitbnkyg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,22 +695,18 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4cqnu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>4184</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>814</v>
+        <v>198</v>
       </c>
       <c r="R3" t="n">
-        <v>4998</v>
+        <v>221</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1602901180</t>
+          <t>37994071</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1602901180</t>
+          <t>https://m.place.naver.com/place/37994071</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24시 피트니스</t>
+          <t>크로스핏BK 혁신점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24hourfitness_@naver.com</t>
+          <t>thlqhd00@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>033-766-4048</t>
+          <t>0507-1439-2177</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 서원대로 474 1, 2층 24시피트니스</t>
+          <t>강원특별자치도 원주시 웅비2길 10 봉우빌딩 B1층 크로스핏BK</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/24hoursfitness2020/?hl=ko</t>
+          <t>https://blog.naver.com/thlqhd00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,19 +789,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4jwb5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>894</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="R4" t="n">
-        <v>1021</v>
+        <v>178</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1016379546</t>
+          <t>1074040282</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1016379546</t>
+          <t>https://m.place.naver.com/place/1074040282</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바디라인휘트니스 원주무실점</t>
+          <t>골드휘트니스 문막점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bodyline2@naver.com</t>
+          <t>gustn7373@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1428-3415</t>
+          <t>0507-1363-2070</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 48-1 5층</t>
+          <t>강원특별자치도 원주시 문막읍 왕건로 46</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,24 +878,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4loqz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>714</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>723</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1437</v>
+        <v>4</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1140023595</t>
+          <t>15256122</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140023595</t>
+          <t>https://m.place.naver.com/place/15256122</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>메가짐 PT&amp;필라테스</t>
+          <t>점핑타임</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>megagym9932@naver.com</t>
+          <t>thinkga76@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1325-9932</t>
+          <t>0507-1497-1101</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 원주시 서원대로 165-3 아트스페이스 5층</t>
+          <t>강원특별자치도 원주시 건강로 17-1 2층 205호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/megagym9932</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,24 +972,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tavv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1716</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>336</v>
+        <v>17</v>
       </c>
       <c r="R6" t="n">
-        <v>2052</v>
+        <v>22</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1302676152</t>
+          <t>1195360217</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302676152</t>
+          <t>https://m.place.naver.com/place/1195360217</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>팀키스짐 &amp; PT</t>
+          <t>코어척추운동센터</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>teamkis_@naver.com</t>
+          <t>kbk9901016@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1399-2305</t>
+          <t>070-7075-7544</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 26 4층</t>
+          <t>강원특별자치도 원주시 만대로 148</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamkis_</t>
+          <t>http://cafe.daum.net/corebodygym0st</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,19 +1071,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4olwd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,17 +1087,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2319</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2819</v>
+        <v>2</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1433616376</t>
+          <t>30820562</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433616376</t>
+          <t>https://m.place.naver.com/place/30820562</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1152,25 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>크로스핏 컴뱃</t>
+          <t>바이브짐 PT&amp;헬스 혁신점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>taiwansister@naver.com</t>
+          <t>vibegym_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1490-3386</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 만대공원길 64 1층</t>
+          <t>강원특별자치도 원주시 세계로 3 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit__combat</t>
+          <t>https://www.instagram.com/vibe_gym_?igsh=MXJnd2FybDBwb3F6OQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1205,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>166</v>
+        <v>118</v>
       </c>
       <c r="Q8" t="n">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="R8" t="n">
-        <v>210</v>
+        <v>272</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,51 +1200,47 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36369149</t>
+          <t>1071680373</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36369149</t>
+          <t>https://m.place.naver.com/place/1071680373</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비브레 PT\u002F헬스 혁신점</t>
+          <t>크로스핏 컴뱃</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wonju_ht@naver.com</t>
+          <t>taiwansister@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1354-8955</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원특별자치도 원주시 만대공원길 64 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://vivre-training.com/</t>
+          <t>https://www.instagram.com/crossfit__combat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1284,14 +1260,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46eja</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>378</v>
+        <v>166</v>
       </c>
       <c r="Q9" t="n">
-        <v>2174</v>
+        <v>44</v>
       </c>
       <c r="R9" t="n">
-        <v>2552</v>
+        <v>210</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,115 +1290,8543 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1193233179</t>
+          <t>36369149</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193233179</t>
+          <t>https://m.place.naver.com/place/36369149</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비플로우PT&amp;그룹PT</t>
+          <t>홍키통키 휘트니스 원주기업도시점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bflowpt@naver.com</t>
+          <t>hongkitongki-@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1437-1576</t>
+          <t>0507-1413-9684</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 9 3층 비플로우</t>
+          <t>강원특별자치도 원주시 지정면 무릉로 35-1 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/hongki_tongki_wonju</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>782</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>409</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1191</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1355839414</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1355839414</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>목욕탕,사우나</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>청담사우나헬스</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ohkfifa@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1482-1126</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 남원로534번길 64</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>29</v>
+      </c>
+      <c r="R11" t="n">
+        <v>350</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1245074192</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1245074192</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>조이클럽멀티짐</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>wldls1129@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>033-766-5516</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 나비허리길 33 3층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/1joyclub</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>20</v>
+      </c>
+      <c r="R12" t="n">
+        <v>48</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1986847768</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1986847768</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>올라운더짐 헬스&amp;PT 무실점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>allrounder_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1359-5382</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 솔우물2길 29-1 3층 올라운더 짐</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/allrounder_gym</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>47</v>
+      </c>
+      <c r="R13" t="n">
+        <v>104</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1497992346</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1497992346</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>스카이짐</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>seee9518@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>033-746-6080</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 남산로 180 8층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/seee9518</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9</v>
+      </c>
+      <c r="R14" t="n">
+        <v>9</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1340553997</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1340553997</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>아이두 PT&amp;그룹PT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>foreverido9993@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1425-0383</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 51 819호,820호,821호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/foreverido9993</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>43</v>
+      </c>
+      <c r="R15" t="n">
+        <v>157</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1973853263</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1973853263</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>커브스 단구클럽</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>weonju007@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1447-4030</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 392 스타프라자 3층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/curvesdangu_</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>16</v>
+      </c>
+      <c r="R16" t="n">
+        <v>69</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>21547560</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21547560</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TK바디브라운 PT&amp;헬스</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>cycnike201@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1339-3020</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 74 7층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cycnike201</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>276</v>
+      </c>
+      <c r="R17" t="n">
+        <v>524</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1209497100</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1209497100</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>원포인트</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>onepointsoccer@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1338-1058</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 원문로 146 3층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>http://cfonepoint.itrocks.kr/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>653</v>
+      </c>
+      <c r="R18" t="n">
+        <v>662</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>36609953</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36609953</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>24시 피트니스</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>24hourfitness_@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1313-4048</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 474 1, 2층 24시피트니스</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/24hoursfitness2020/?hl=ko</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>908</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>127</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1035</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1016379546</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1016379546</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>펄핏 스튜디오 PT/헬스</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gomete6363@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1389-9039</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 천매봉길 32-22 2층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pearl_fit_</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>124</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>368</v>
+      </c>
+      <c r="R20" t="n">
+        <v>492</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1471872878</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1471872878</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>팀키스짐 &amp; PT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>teamkis_@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1399-2305</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 26 4층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teamkis_</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>2326</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>500</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2826</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1433616376</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1433616376</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>VIP FITNESS 세경점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jaesoung12345@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>033-742-0433</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 단구로 424 세경웰러스상가 301호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>83</v>
+      </c>
+      <c r="R22" t="n">
+        <v>106</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1329264100</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1329264100</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>제이엠피트니스</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>deny7004@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>033-733-3336</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 건강로 17 스타타워2. 5층 502호 503호 504호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/deny7004</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>15</v>
+      </c>
+      <c r="R23" t="n">
+        <v>47</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2005941753</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2005941753</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>문막HM휘트니스</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>hm_7777@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1397-5874</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 문막읍 원문로 1595 2층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hm_7777</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>13</v>
+      </c>
+      <c r="R24" t="n">
+        <v>65</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1023016392</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1023016392</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>이룸바디스튜디오</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ghghgh2440@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1412-2449</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 백간길 55 2층 이룸바디스튜디오</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sYsj3q3c</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>40</v>
+      </c>
+      <c r="R25" t="n">
+        <v>107</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1611359768</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1611359768</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>오디세이 피트니스</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>compuzonestory@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1320-7697</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 72 센트럴프라자2, 501호~504호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/odysseyfitness.kr/</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2021582889</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2021582889</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>블랑꼬 PT&amp;헬스 기업도시점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>dlarhkddbf1@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 신지정로 316-1 4층(골드파크빌딩)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dlarhkddbf1</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>269</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>165</v>
+      </c>
+      <c r="R27" t="n">
+        <v>434</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1401069241</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1401069241</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>해피짐 헬스&amp;PT 원주혁신점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0226juj@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1336-7769</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 봉황2길 17 3층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/happygym_official/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>96</v>
+      </c>
+      <c r="R28" t="n">
+        <v>154</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2041898786</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2041898786</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>호크아이짐 헬스/PT/태닝</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>hawkeyegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1307-5822</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 106 3층 호크아이짐</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hawkeyegym</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>4207</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>815</v>
+      </c>
+      <c r="R29" t="n">
+        <v>5022</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1602901180</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1602901180</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>블루짐</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>bluegym_2412@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1443-7200</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 백간길 55 101-4호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bluegym_2412</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1335716320</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1335716320</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>상아휘트니스</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ablegym9@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>033-747-6398</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 바우골길 8 프렌티어스빌딩5층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>9</v>
+      </c>
+      <c r="R31" t="n">
+        <v>24</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>15214867</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15214867</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>로드짐</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>moolbar@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>033-744-2626</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 37-2 5층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/moolbar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>38</v>
+      </c>
+      <c r="R32" t="n">
+        <v>42</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1538542519</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1538542519</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>하이컴뱃</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>taiwansister@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1347-5120</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 송삼길 19 1층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hycombat__</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>32</v>
+      </c>
+      <c r="R33" t="n">
+        <v>37</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2058886633</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2058886633</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>원주국제걷기대회</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>mmsus2392@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>kwf@walking.kr</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>033-762-2234</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 단구로 170 원주따뚜공연장</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>http://www.koreawalk.kr/</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>18</v>
+      </c>
+      <c r="R34" t="n">
+        <v>24</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>13045168</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13045168</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HM 휘트니스</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>hm_7777@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1392-5874</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 396 2층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hm_7777</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>119</v>
+      </c>
+      <c r="R35" t="n">
+        <v>216</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>51291896</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/51291896</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>몬스터짐 요가&amp;PT헬스</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>chlwlgns6138@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1474-3328</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 건강로 23 4층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/chlwlgns6138</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>10</v>
+      </c>
+      <c r="R36" t="n">
+        <v>15</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2041484449</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2041484449</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>더에스짐</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>thesgym3736@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1442-0884</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 영랑길 13 그린빌딩 7층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2043004666</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2043004666</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>훈짐 원주점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>hoongym@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>033-766-8221</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥업면 남원로 52-5 1층, 2층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hoongym</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>216</v>
+      </c>
+      <c r="R38" t="n">
+        <v>273</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1943954995</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1943954995</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>히든헬스클럽</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jayttt@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>033-762-1120</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 무실로 189 2층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jayttt</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>100</v>
+      </c>
+      <c r="R39" t="n">
+        <v>124</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>38278726</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38278726</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>크로스핏에임 혁신점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>tafjq1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1319-5745</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 39-2 1층 107호, 108호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>7</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1853505932</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853505932</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>유진헬스클럽</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>insightmedia@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>033-761-5959</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 황소마을길 40</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>19</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>11679515</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11679515</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>헬스붐</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>wkdwnel4@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>033-734-9061</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥양로51번길 108</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>18</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>15282839</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15282839</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>엠투짐</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>k1140391@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1358-1467</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 39-2 서울메디컬센터 5층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/m2gym.spinning</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>28</v>
+      </c>
+      <c r="R43" t="n">
+        <v>207</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>37912788</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37912788</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>비브레 PT/헬스 혁신점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>wonju_ht@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1354-8955</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 건강로 17-2 6층 601~604호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>http://vivre-training.com/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>378</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2178</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2556</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1193233179</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1193233179</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>반곡뮤직스피닝</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>zkscy293@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1335-4279</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 늘품로 187-58 현대아카데미 5층 뮤직스피닝</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/musicspinning_bangok?igsh=MW55NGxzaHFrZG4yZw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>19</v>
+      </c>
+      <c r="R45" t="n">
+        <v>62</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1766314585</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1766314585</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ROAD GYM</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ghsk52@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>033-743-6766</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 시청로 80 쎈터프라자 10층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ghsk52</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>101</v>
+      </c>
+      <c r="R46" t="n">
+        <v>104</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>15247473</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15247473</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>커브스 무실클럽</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>sputnik23@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>033-742-7330</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 시청로 80 쎈터프라자 3층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sputnik23</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>9</v>
+      </c>
+      <c r="R47" t="n">
+        <v>63</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>36538620</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36538620</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>스타트라인 혁신점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>startupkised@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1344-3599</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 웅비1길 12-1 1층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/origin_wan?igsh=ajJwN201dXJham9p</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>4</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1296426839</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1296426839</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>비타민헬스클럽</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>shichichi@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>033-746-7494</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥양로18번길 33</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>16</v>
+      </c>
+      <c r="R49" t="n">
+        <v>76</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>15282842</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15282842</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>비엔케이피트니스클럽</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>flavorhunter_@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 나비허리길 97</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1797081807</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1797081807</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>하디웨이트짐</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>hardyweightgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1334-8501</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 천사로 178 지하1층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hardyweightgym</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2034880654</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2034880654</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>더바른PT / 헬스 혁신점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>thebarnnpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1491-1113</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 53 4층 더바른PT</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thebarnnpt</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>242</v>
+      </c>
+      <c r="R52" t="n">
+        <v>421</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1850025502</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850025502</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>원주인터불고 웰니스센터</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>yjw5443@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>033-769-8201</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 동부순환로 200</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>12</v>
+      </c>
+      <c r="R53" t="n">
+        <v>83</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1339846931</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1339846931</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>리온 휘트니스</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>reon_fitness1@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1369-8925</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 문막읍 왕건로 81 3층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/reon_fitness1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>167</v>
+      </c>
+      <c r="R54" t="n">
+        <v>392</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1876515774</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1876515774</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>바디라인휘트니스 원주무실점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>bodyline2@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1428-3415</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyline2</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>717</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>727</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1444</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1140023595</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1140023595</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>오짐 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>wonjuogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1406-2506</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 모란1길 69 3층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wonjuogym</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>4009</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>364</v>
+      </c>
+      <c r="R56" t="n">
+        <v>4373</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1101731614</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1101731614</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>엔터핏헬스&amp;골프</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>enterfit_wonju@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1424-8254</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 입춘로 69 4층 401호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/enterfit_wonju/223823197126</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>279</v>
+      </c>
+      <c r="R57" t="n">
+        <v>335</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1866503944</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1866503944</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>무실동 듀플릿 헬스/PT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jin10240107@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1306-6059</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 70 5층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jin10240107</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>3507</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>740</v>
+      </c>
+      <c r="R58" t="n">
+        <v>4247</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1659772512</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1659772512</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>점핑스피닝GX</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>dessing34@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>033-813-0051</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 반곡초교로 77-2</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>5</v>
+      </c>
+      <c r="R59" t="n">
+        <v>11</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1972135147</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1972135147</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>블랑꼬 PT&amp;헬스 태장점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>dlarhkddbf1@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1330-4023</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥양로18번길 35 . 지하 1층&amp;2층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dlarhkddbf1</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>59</v>
+      </c>
+      <c r="R60" t="n">
+        <v>143</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1901538636</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1901538636</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>엑스스피닝</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>spinning1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1361-2234</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 51 시네시티타워 6층 619호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spinning1004</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>38</v>
+      </c>
+      <c r="R61" t="n">
+        <v>61</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1195598010</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1195598010</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>저스트포짐</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>24hourfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1472-1476</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 황금로 20 404호 저스트포짐</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/13/bizes/1409591</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>182</v>
+      </c>
+      <c r="R62" t="n">
+        <v>209</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1943100672</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1943100672</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>대동헬스피아</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>onsi09@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>033-748-3279</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 북원상가길 13 북원상가 3층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://ok114.co.kr/0337483279</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>6</v>
+      </c>
+      <c r="R63" t="n">
+        <v>12</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>15282840</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15282840</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>월드헬스휘트니스</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>yun3392@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>033-746-9977</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 문막읍 왕건로 22</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>19928385</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19928385</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>메가짐 PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>megagym9932@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1325-9932</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 165-3 아트스페이스 5층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/megagym9932</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1726</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>336</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2062</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1302676152</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1302676152</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>더피티라운지</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>the_pt_lounge@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1327-2648</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 버들만이길 3-1 1층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_mbYxbb</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>42</v>
+      </c>
+      <c r="R66" t="n">
+        <v>129</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1798078297</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1798078297</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>피지컬짐</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>physicalgym03@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1422-6460</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 37-1 반곡빌딩 3층 301호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/physicalgym03</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2</v>
+      </c>
+      <c r="R67" t="n">
+        <v>13</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1324996335</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1324996335</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>핏앤피트니스 PT &amp; 그룹피티 기업점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>rlghks405@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1328-0301</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 신지정로 172 6층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlghks405</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>292</v>
+      </c>
+      <c r="R68" t="n">
+        <v>395</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1139721387</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1139721387</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>다이아짐</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>top-health@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1428-5618</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 37 302호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>3</v>
+      </c>
+      <c r="R69" t="n">
+        <v>3</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1877473254</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1877473254</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>OK시니어체인지클럽</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>okscc-@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1481-0006</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 402 4층 402호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://연세오케이정형외과.kr/ok-change-club</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>77</v>
+      </c>
+      <c r="R70" t="n">
+        <v>88</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>2086283255</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2086283255</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>바디아카데미 PT 프리미엄센터</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>dlrlckdtkdwl@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>033-900-7450</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 34-1 센트럴프라자 3차 3층 바디아카데미 PT 프리미엄센터</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ki_chang_l/</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>593</v>
+      </c>
+      <c r="R71" t="n">
+        <v>680</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1329553206</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1329553206</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>바디아카데미 기업도시점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>juseokchan91@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1393-4411</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 신지정로 212 롯데퍼스트프라자 6층 바디아카데미</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>145</v>
+      </c>
+      <c r="R72" t="n">
+        <v>151</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1896388555</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1896388555</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>비브레 프리미엄점 PT &amp; 필라테스</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>wonju_ht@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 건강로 17-2 5층 ( 501~502호)</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>http://vivre-training.com/</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>627</v>
+      </c>
+      <c r="R73" t="n">
+        <v>911</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1370848344</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1370848344</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>핏앤피트니스 혁신점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ssb154911@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>033-735-0302</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 미래로 1 강림빌딩 3층 302호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://fitandfitness.imweb.me</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>284</v>
+      </c>
+      <c r="R74" t="n">
+        <v>406</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1042681042</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1042681042</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>본움 체형교정 선수트레이닝 센터</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>rlghks00235@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1336-1466</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 미래로 1 3층 303호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlghks00235</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>48</v>
+      </c>
+      <c r="R75" t="n">
+        <v>56</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2088505203</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2088505203</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>핏앤피트니스 PT &amp; 그룹피티</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ssz1549@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1445-0383</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 47 8층,핏앤피트니스</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@hipupschool</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>778</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1016</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1793276177</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1793276177</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>엑스바디 PT 스튜디오 무실동</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>xbody1101@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 시청로 86 부영골든빌 4층 403호</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/x.body_ptstudio</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>316</v>
+      </c>
+      <c r="R77" t="n">
+        <v>432</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1571856002</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1571856002</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>몸수선토탈케어PT샵</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>dmsal04@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1423-0830</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 천매봉길 58 1층</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/momsuseon?igsh=d3NiM3MwNTYzaXA4</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>37</v>
+      </c>
+      <c r="R78" t="n">
+        <v>37</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1964597317</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1964597317</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>네츄럴 올림피아</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ojg4205@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>033-732-0035</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 시청로 160-1 노블인갤러리 2F (법원맞은편)</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>3</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>31674353</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31674353</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>혁신런앤핏</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>hghghghg00@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1346-7262</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 19 지하층 101호</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hs_run_fit</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>23</v>
+      </c>
+      <c r="R80" t="n">
+        <v>23</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1223719800</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1223719800</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>율핏피트니스 PT센터 무실점</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>yulgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 65 휴먼타워 9층 902호 903호 (무실동 1857-1)</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yulgym</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>486</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>522</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1008</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>481098140</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/481098140</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>리햅포먼스</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>rehabformance@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1324-4662</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 만대로 166 4층 리햅포먼스</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rehabformance</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>71</v>
+      </c>
+      <c r="R82" t="n">
+        <v>131</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1229524729</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1229524729</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>컨피던스짐 단구점</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>confidencegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1348-9679</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 남원로534번길 51 2층</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/confidence_1st</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>319</v>
+      </c>
+      <c r="R83" t="n">
+        <v>439</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1250040920</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1250040920</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>바디아카데미 혁신도시점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>wkdgusxo12345@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1493-4412</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 양지로 20 오썸파크 209호</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/body___academy_ht</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>86</v>
+      </c>
+      <c r="R84" t="n">
+        <v>154</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1128838469</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1128838469</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>조거앤스웨트</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>woonduong@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1447-9913</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 35 202호</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jogger_sweat</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>16</v>
+      </c>
+      <c r="R85" t="n">
+        <v>28</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1412402393</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1412402393</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>원주무실동프리미엄피티</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>h__a843@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 로아노크로 76 1층</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>3</v>
+      </c>
+      <c r="R86" t="n">
+        <v>18</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1217507491</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1217507491</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>헤이스바디랩</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>heisbodylab@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0506-571-3069</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥양로51번길 1 원마트 2층</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/heis_body_lab</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>205</v>
+      </c>
+      <c r="R87" t="n">
+        <v>211</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1399142746</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1399142746</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>스노블트레이닝PT센터</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>igtrainer@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1349-8857</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 황금로 29 4층 401호</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@youreyelevel</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>88</v>
+      </c>
+      <c r="R88" t="n">
+        <v>110</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>2028571477</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2028571477</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>컨피던스짐 원주 단계점</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>heyoungshin@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1444-9680</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 단구로 80 1층</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>29</v>
+      </c>
+      <c r="R89" t="n">
+        <v>53</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1341284821</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1341284821</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>바디팩토리웰니스짐</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>rntjdah2@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 만대로 158</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rntjdah2</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>55</v>
+      </c>
+      <c r="R90" t="n">
+        <v>55</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>35958713</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35958713</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>클래식짐 PT 혁신점</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>classicgym2749@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1313-2749</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 황금로 20 5층 502호</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/classicgym2749</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>84</v>
+      </c>
+      <c r="R91" t="n">
+        <v>160</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1324878145</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1324878145</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>다르짐</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>lozebons@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1358-9021</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 섬밭들1길 26-9 1층 다르짐</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/runner_dar/</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>2</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1344578636</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1344578636</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>비플로우PT&amp;그룹PT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>bflowpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1437-1576</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 9 3층 비플로우</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
           <t>https://blog.naver.com/bflowpt</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h9q7</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
         <v>235</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q93" t="n">
         <v>664</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R93" t="n">
         <v>899</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
         <is>
           <t>1870827414</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1870827414</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>앤비 프라이빗 짐</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>johnkhong13@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>033-732-5777</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 건강로 25 서영 에비뉴파크 1차 602호</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/johnkhong13</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>13</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>37676393</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37676393</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>노익스짐 PT</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>no_x_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1486-6692</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 무실본동길 38 1층 노익스짐</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/no_x_gym</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>864</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1151</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1213015794</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213015794</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>실내체육관</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>원주시농민문화체육센터</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>033-737-4725</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 문막읍 건등로 21 농민문화체육센터</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://yeyak.wonju.go.kr/www/main.do</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>48</v>
+      </c>
+      <c r="R96" t="n">
+        <v>174</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>21387721</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21387721</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>실내체육관</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>원주남부 복합체육센터</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>wjkk87@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>033-737-4955</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 이화5길 70</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://www.wonju.go.kr/www/contents.do?key=6028&amp;</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>83</v>
+      </c>
+      <c r="R97" t="n">
+        <v>111</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1282336869</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1282336869</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>실내체육관</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>원주드림체육관</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>anaber@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>033-737-4666</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 현충로 53-1 원주드림체육관</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://www.wonju.go.kr/facility/contents.do?key=6385&amp;</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>43</v>
+      </c>
+      <c r="R98" t="n">
+        <v>163</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>34605311</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34605311</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>요가,명상</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>지성요가원</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>wonju_jisung_yoga@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1401-0382</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 시청로 94 보네르 빌딩 4층 지성요가원</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jisung_yoga_wonju/</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>59</v>
+      </c>
+      <c r="R99" t="n">
+        <v>146</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>31992339</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31992339</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>체육관</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>에임크로스핏</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>newtriple@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1415-6004</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 북원로 1897 1층~2층</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/aim_crossfit</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>150</v>
+      </c>
+      <c r="R100" t="n">
+        <v>155</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>1062060537</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1062060537</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/원주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/원주_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V100"/>
+  <dimension ref="A1:V82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이스스포츠센터&amp;에이스짐PT</t>
+          <t>더바른PT / 헬스 혁신점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jth3824@naver.com</t>
+          <t>thebarnnpt@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1336-5769</t>
+          <t>0507-1491-1113</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 원일로115번길 16 4층</t>
+          <t>강원특별자치도 원주시 혁신로 53 4층 더바른PT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/acegym_wonju</t>
+          <t>https://blog.naver.com/thebarnnpt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1583</v>
+        <v>179</v>
       </c>
       <c r="Q2" t="n">
-        <v>919</v>
+        <v>242</v>
       </c>
       <c r="R2" t="n">
-        <v>2502</v>
+        <v>421</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>15201329</t>
+          <t>1850025502</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15201329</t>
+          <t>https://m.place.naver.com/place/1850025502</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>크로스핏BnK</t>
+          <t>원주인터불고 웰니스센터</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dldbsrnjs11@naver.com</t>
+          <t>yjw5443@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1359-0221</t>
+          <t>033-769-8201</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 나비허리길 97 2동 1층</t>
+          <t>강원특별자치도 원주시 동부순환로 200</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfitbnkyg</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="Q3" t="n">
-        <v>198</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>37994071</t>
+          <t>1339846931</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37994071</t>
+          <t>https://m.place.naver.com/place/1339846931</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>크로스핏BK 혁신점</t>
+          <t>문막HM휘트니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>thlqhd00@naver.com</t>
+          <t>hm_7777@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1439-2177</t>
+          <t>0507-1397-5874</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 웅비2길 10 봉우빌딩 B1층 크로스핏BK</t>
+          <t>강원특별자치도 원주시 문막읍 원문로 1595 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thlqhd00</t>
+          <t>https://blog.naver.com/hm_7777</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="Q4" t="n">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1074040282</t>
+          <t>1023016392</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1074040282</t>
+          <t>https://m.place.naver.com/place/1023016392</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>골드휘트니스 문막점</t>
+          <t>팀키스짐 &amp; PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gustn7373@naver.com</t>
+          <t>teamkis_@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1363-2070</t>
+          <t>0507-1399-2305</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 문막읍 왕건로 46</t>
+          <t>강원특별자치도 원주시 능라동길 26 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/teamkis_</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2326</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>2826</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>15256122</t>
+          <t>1433616376</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15256122</t>
+          <t>https://m.place.naver.com/place/1433616376</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,24 +940,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>점핑타임</t>
+          <t>헬스붐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>thinkga76@naver.com</t>
+          <t>wkdwnel4@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1497-1101</t>
+          <t>033-734-9061</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 건강로 17-1 2층 205호</t>
+          <t>강원특별자치도 원주시 흥양로51번길 108</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1195360217</t>
+          <t>15282839</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1195360217</t>
+          <t>https://m.place.naver.com/place/15282839</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>코어척추운동센터</t>
+          <t>바이브짐 PT&amp;헬스 혁신점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kbk9901016@naver.com</t>
+          <t>vibegym_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>070-7075-7544</t>
+          <t>0507-1490-3386</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 만대로 148</t>
+          <t>강원특별자치도 원주시 세계로 3 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://cafe.daum.net/corebodygym0st</t>
+          <t>https://www.instagram.com/vibe_gym_?igsh=MXJnd2FybDBwb3F6OQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>272</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>30820562</t>
+          <t>1071680373</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30820562</t>
+          <t>https://m.place.naver.com/place/1071680373</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,34 +1123,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바이브짐 PT&amp;헬스 혁신점</t>
+          <t>올라운더짐 헬스&amp;PT 무실점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>vibegym_@naver.com</t>
+          <t>allrounder_gym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1490-3386</t>
+          <t>0507-1359-5382</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 세계로 3 3층</t>
+          <t>강원특별자치도 원주시 솔우물2길 29-1 3층 올라운더 짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vibe_gym_?igsh=MXJnd2FybDBwb3F6OQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/allrounder_gym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>118</v>
+        <v>57</v>
       </c>
       <c r="Q8" t="n">
-        <v>154</v>
+        <v>47</v>
       </c>
       <c r="R8" t="n">
-        <v>272</v>
+        <v>104</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1071680373</t>
+          <t>1497992346</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071680373</t>
+          <t>https://m.place.naver.com/place/1497992346</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,25 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>크로스핏 컴뱃</t>
+          <t>몬스터짐 요가&amp;PT헬스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>taiwansister@naver.com</t>
+          <t>chlwlgns6138@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1474-3328</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 만대공원길 64 1층</t>
+          <t>강원특별자치도 원주시 건강로 23 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit__combat</t>
+          <t>https://blog.naver.com/chlwlgns6138</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>166</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>210</v>
+        <v>15</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36369149</t>
+          <t>2041484449</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36369149</t>
+          <t>https://m.place.naver.com/place/2041484449</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1312,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>홍키통키 휘트니스 원주기업도시점</t>
+          <t>엔터핏헬스&amp;골프</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hongkitongki-@naver.com</t>
+          <t>enterfit_wonju@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1413-9684</t>
+          <t>0507-1424-8254</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 지정면 무릉로 35-1 3층</t>
+          <t>강원특별자치도 원주시 입춘로 69 4층 401호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hongki_tongki_wonju</t>
+          <t>https://blog.naver.com/enterfit_wonju/223823197126</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>782</v>
+        <v>56</v>
       </c>
       <c r="Q10" t="n">
-        <v>409</v>
+        <v>279</v>
       </c>
       <c r="R10" t="n">
-        <v>1191</v>
+        <v>335</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1355839414</t>
+          <t>1866503944</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1355839414</t>
+          <t>https://m.place.naver.com/place/1866503944</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1401,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>목욕탕,사우나</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>청담사우나헬스</t>
+          <t>24시 피트니스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ohkfifa@naver.com</t>
+          <t>24hourfitness_@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1482-1126</t>
+          <t>0507-1313-4048</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 남원로534번길 64</t>
+          <t>강원특별자치도 원주시 서원대로 474 1, 2층 24시피트니스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/24hoursfitness2020/?hl=ko</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1438,7 +1442,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1459,17 +1463,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>321</v>
+        <v>908</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="R11" t="n">
-        <v>350</v>
+        <v>1035</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1245074192</t>
+          <t>1016379546</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245074192</t>
+          <t>https://m.place.naver.com/place/1016379546</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1589,34 +1593,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>올라운더짐 헬스&amp;PT 무실점</t>
+          <t>훈짐 원주점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>allrounder_gym@naver.com</t>
+          <t>hoongym@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1359-5382</t>
+          <t>033-766-8221</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 솔우물2길 29-1 3층 올라운더 짐</t>
+          <t>강원특별자치도 원주시 흥업면 남원로 52-5 1층, 2층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/allrounder_gym</t>
+          <t>https://blog.naver.com/hoongym</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1654,10 +1658,10 @@
         <v>57</v>
       </c>
       <c r="Q13" t="n">
-        <v>47</v>
+        <v>216</v>
       </c>
       <c r="R13" t="n">
-        <v>104</v>
+        <v>273</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,12 +1670,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1497992346</t>
+          <t>1943954995</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1497992346</t>
+          <t>https://m.place.naver.com/place/1943954995</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1688,29 +1692,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>스카이짐</t>
+          <t>바디라인휘트니스 원주무실점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>seee9518@naver.com</t>
+          <t>bodyline2@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>033-746-6080</t>
+          <t>0507-1428-3415</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 남산로 180 8층</t>
+          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/seee9518</t>
+          <t>https://blog.naver.com/bodyline2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1741,17 +1745,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>729</v>
       </c>
       <c r="R14" t="n">
-        <v>9</v>
+        <v>1446</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,12 +1764,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1340553997</t>
+          <t>1140023595</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340553997</t>
+          <t>https://m.place.naver.com/place/1140023595</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1782,34 +1786,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아이두 PT&amp;그룹PT</t>
+          <t>원포인트</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>foreverido9993@naver.com</t>
+          <t>onepointsoccer@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1425-0383</t>
+          <t>0507-1338-1058</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 51 819호,820호,821호</t>
+          <t>강원특별자치도 원주시 원문로 146 3층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/foreverido9993</t>
+          <t>http://cfonepoint.itrocks.kr/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1819,7 +1823,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1835,17 +1839,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>114</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>43</v>
+        <v>653</v>
       </c>
       <c r="R15" t="n">
-        <v>157</v>
+        <v>662</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,12 +1858,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1973853263</t>
+          <t>36609953</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973853263</t>
+          <t>https://m.place.naver.com/place/36609953</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1876,29 +1880,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>커브스 단구클럽</t>
+          <t>홍키통키 휘트니스 원주기업도시점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>weonju007@naver.com</t>
+          <t>hongkitongki-@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1447-4030</t>
+          <t>0507-1413-9684</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 서원대로 392 스타프라자 3층</t>
+          <t>강원특별자치도 원주시 지정면 무릉로 35-1 3층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/curvesdangu_</t>
+          <t>https://www.instagram.com/hongki_tongki_wonju</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1933,13 +1937,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>53</v>
+        <v>782</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>409</v>
       </c>
       <c r="R16" t="n">
-        <v>69</v>
+        <v>1191</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,12 +1952,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>21547560</t>
+          <t>1355839414</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21547560</t>
+          <t>https://m.place.naver.com/place/1355839414</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1965,34 +1969,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TK바디브라운 PT&amp;헬스</t>
+          <t>하디웨이트짐</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cycnike201@naver.com</t>
+          <t>hardyweightgym@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1339-3020</t>
+          <t>0507-1334-8501</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 74 7층</t>
+          <t>강원특별자치도 원주시 천사로 178 지하1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cycnike201</t>
+          <t>https://blog.naver.com/hardyweightgym</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2007,7 +2011,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2023,17 +2027,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>524</v>
+        <v>1</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,12 +2046,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1209497100</t>
+          <t>2034880654</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1209497100</t>
+          <t>https://m.place.naver.com/place/2034880654</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2064,39 +2068,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>원포인트</t>
+          <t>대동헬스피아</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>onepointsoccer@naver.com</t>
+          <t>onsi09@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1338-1058</t>
+          <t>033-748-3279</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 원문로 146 3층</t>
+          <t>강원특별자치도 원주시 북원상가길 13 북원상가 3층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://cfonepoint.itrocks.kr/</t>
+          <t>https://ok114.co.kr/0337483279</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2121,13 +2125,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
-        <v>653</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>662</v>
+        <v>12</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,12 +2140,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>36609953</t>
+          <t>15282840</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36609953</t>
+          <t>https://m.place.naver.com/place/15282840</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2153,34 +2157,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24시 피트니스</t>
+          <t>비브레 PT/헬스 혁신점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>24hourfitness_@naver.com</t>
+          <t>wonju_ht@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1313-4048</t>
+          <t>0507-1354-8955</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 서원대로 474 1, 2층 24시피트니스</t>
+          <t>강원특별자치도 원주시 건강로 17-2 6층 601~604호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/24hoursfitness2020/?hl=ko</t>
+          <t>http://vivre-training.com/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2215,13 +2219,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>908</v>
+        <v>378</v>
       </c>
       <c r="Q19" t="n">
-        <v>127</v>
+        <v>2178</v>
       </c>
       <c r="R19" t="n">
-        <v>1035</v>
+        <v>2556</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,12 +2234,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1016379546</t>
+          <t>1193233179</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1016379546</t>
+          <t>https://m.place.naver.com/place/1193233179</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2247,34 +2251,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>펄핏 스튜디오 PT/헬스</t>
+          <t>로드짐</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>gomete6363@naver.com</t>
+          <t>moolbar@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1389-9039</t>
+          <t>033-744-2626</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 천매봉길 32-22 2층</t>
+          <t>강원특별자치도 원주시 혁신로 37-2 5층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pearl_fit_</t>
+          <t>https://blog.naver.com/moolbar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2289,7 +2293,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2305,17 +2309,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>124</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
-        <v>368</v>
+        <v>38</v>
       </c>
       <c r="R20" t="n">
-        <v>492</v>
+        <v>42</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,12 +2328,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1471872878</t>
+          <t>1538542519</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471872878</t>
+          <t>https://m.place.naver.com/place/1538542519</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2346,29 +2350,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>팀키스짐 &amp; PT</t>
+          <t>엠투짐</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>teamkis_@naver.com</t>
+          <t>k1140391@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1399-2305</t>
+          <t>0507-1358-1467</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 26 4층</t>
+          <t>강원특별자치도 원주시 혁신로 39-2 서울메디컬센터 5층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamkis_</t>
+          <t>https://www.instagram.com/m2gym.spinning</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2383,7 +2387,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2403,13 +2407,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2326</v>
+        <v>179</v>
       </c>
       <c r="Q21" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="R21" t="n">
-        <v>2826</v>
+        <v>207</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,12 +2422,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1433616376</t>
+          <t>37912788</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433616376</t>
+          <t>https://m.place.naver.com/place/37912788</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2534,29 +2538,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>제이엠피트니스</t>
+          <t>점핑스피닝GX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>deny7004@naver.com</t>
+          <t>dessing34@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>033-733-3336</t>
+          <t>033-813-0051</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 건강로 17 스타타워2. 5층 502호 503호 504호</t>
+          <t>강원특별자치도 원주시 반곡초교로 77-2</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/deny7004</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2566,12 +2570,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2591,13 +2595,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2606,12 +2610,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2005941753</t>
+          <t>1972135147</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2005941753</t>
+          <t>https://m.place.naver.com/place/1972135147</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2628,29 +2632,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>문막HM휘트니스</t>
+          <t>ROAD GYM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hm_7777@naver.com</t>
+          <t>ghsk52@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1397-5874</t>
+          <t>033-743-6766</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 문막읍 원문로 1595 2층</t>
+          <t>강원특별자치도 원주시 시청로 80 쎈터프라자 10층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hm_7777</t>
+          <t>https://blog.naver.com/ghsk52</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2681,17 +2685,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="R24" t="n">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2700,12 +2704,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1023016392</t>
+          <t>15247473</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023016392</t>
+          <t>https://m.place.naver.com/place/15247473</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2722,29 +2726,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>이룸바디스튜디오</t>
+          <t>커브스 무실클럽</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ghghgh2440@naver.com</t>
+          <t>sputnik23@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1412-2449</t>
+          <t>033-742-7330</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 백간길 55 2층 이룸바디스튜디오</t>
+          <t>강원특별자치도 원주시 시청로 80 쎈터프라자 3층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sYsj3q3c</t>
+          <t>https://blog.naver.com/sputnik23</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2759,7 +2763,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2770,22 +2774,22 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="R25" t="n">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2794,12 +2798,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1611359768</t>
+          <t>36538620</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611359768</t>
+          <t>https://m.place.naver.com/place/36538620</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2816,29 +2820,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>오디세이 피트니스</t>
+          <t>해피짐 헬스&amp;PT 원주혁신점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>compuzonestory@naver.com</t>
+          <t>0226juj@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1320-7697</t>
+          <t>0507-1336-7769</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 72 센트럴프라자2, 501호~504호</t>
+          <t>강원특별자치도 원주시 봉황2길 17 3층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/odysseyfitness.kr/</t>
+          <t>https://www.instagram.com/happygym_official/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2873,13 +2877,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2888,12 +2892,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2021582889</t>
+          <t>2041898786</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021582889</t>
+          <t>https://m.place.naver.com/place/2041898786</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2910,25 +2914,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>블랑꼬 PT&amp;헬스 기업도시점</t>
+          <t>크로스핏BnK</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dlarhkddbf1@naver.com</t>
+          <t>dldbsrnjs11@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1359-0221</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 지정면 신지정로 316-1 4층(골드파크빌딩)</t>
+          <t>강원특별자치도 원주시 나비허리길 97 2동 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlarhkddbf1</t>
+          <t>https://www.instagram.com/crossfitbnkyg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2943,7 +2951,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2963,13 +2971,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>269</v>
+        <v>23</v>
       </c>
       <c r="Q27" t="n">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="R27" t="n">
-        <v>434</v>
+        <v>221</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,12 +2986,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1401069241</t>
+          <t>37994071</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1401069241</t>
+          <t>https://m.place.naver.com/place/37994071</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3000,29 +3008,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>해피짐 헬스&amp;PT 원주혁신점</t>
+          <t>오짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0226juj@naver.com</t>
+          <t>wonjuogym@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1336-7769</t>
+          <t>0507-1406-2506</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 봉황2길 17 3층</t>
+          <t>강원특별자치도 원주시 모란1길 69 3층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/happygym_official/</t>
+          <t>https://blog.naver.com/wonjuogym</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3037,7 +3045,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3057,13 +3065,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>58</v>
+        <v>4009</v>
       </c>
       <c r="Q28" t="n">
-        <v>96</v>
+        <v>364</v>
       </c>
       <c r="R28" t="n">
-        <v>154</v>
+        <v>4373</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,12 +3080,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2041898786</t>
+          <t>1101731614</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2041898786</t>
+          <t>https://m.place.naver.com/place/1101731614</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3094,34 +3102,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>호크아이짐 헬스/PT/태닝</t>
+          <t>이룸바디스튜디오</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>hawkeyegym@naver.com</t>
+          <t>ghghgh2440@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1307-5822</t>
+          <t>0507-1412-2449</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 서원대로 106 3층 호크아이짐</t>
+          <t>강원특별자치도 원주시 백간길 55 2층 이룸바디스튜디오</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hawkeyegym</t>
+          <t>https://open.kakao.com/o/sYsj3q3c</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3131,7 +3139,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3151,13 +3159,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4207</v>
+        <v>67</v>
       </c>
       <c r="Q29" t="n">
-        <v>815</v>
+        <v>40</v>
       </c>
       <c r="R29" t="n">
-        <v>5022</v>
+        <v>107</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,12 +3174,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1602901180</t>
+          <t>1611359768</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1602901180</t>
+          <t>https://m.place.naver.com/place/1611359768</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3188,29 +3196,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>블루짐</t>
+          <t>비엔케이피트니스클럽</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bluegym_2412@naver.com</t>
+          <t>flavorhunter_@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1443-7200</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 백간길 55 101-4호</t>
+          <t>강원특별자치도 원주시 나비허리길 97</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bluegym_2412</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3220,12 +3224,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3241,17 +3245,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,12 +3264,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1335716320</t>
+          <t>1797081807</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335716320</t>
+          <t>https://m.place.naver.com/place/1797081807</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3282,29 +3286,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>상아휘트니스</t>
+          <t>하이컴뱃</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ablegym9@naver.com</t>
+          <t>taiwansister@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>033-747-6398</t>
+          <t>0507-1347-5120</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 바우골길 8 프렌티어스빌딩5층</t>
+          <t>강원특별자치도 원주시 송삼길 19 1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hycombat__</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3314,7 +3318,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3335,17 +3339,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="R31" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3354,12 +3358,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>15214867</t>
+          <t>2058886633</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15214867</t>
+          <t>https://m.place.naver.com/place/2058886633</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3376,29 +3380,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>로드짐</t>
+          <t>메가짐 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>moolbar@naver.com</t>
+          <t>megagym9932@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>033-744-2626</t>
+          <t>0507-1325-9932</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 혁신로 37-2 5층</t>
+          <t>강원특별자치도 원주시 서원대로 165-3 아트스페이스 5층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/moolbar</t>
+          <t>https://blog.naver.com/megagym9932</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3429,17 +3433,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>1726</v>
       </c>
       <c r="Q32" t="n">
-        <v>38</v>
+        <v>336</v>
       </c>
       <c r="R32" t="n">
-        <v>42</v>
+        <v>2062</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3448,12 +3452,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1538542519</t>
+          <t>1302676152</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538542519</t>
+          <t>https://m.place.naver.com/place/1302676152</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3470,29 +3474,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>하이컴뱃</t>
+          <t>유진헬스클럽</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>taiwansister@naver.com</t>
+          <t>insightmedia@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1347-5120</t>
+          <t>033-761-5959</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 송삼길 19 1층</t>
+          <t>강원특별자치도 원주시 황소마을길 40</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hycombat__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3502,7 +3506,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3523,17 +3527,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q33" t="n">
         <v>5</v>
       </c>
-      <c r="Q33" t="n">
-        <v>32</v>
-      </c>
       <c r="R33" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3542,12 +3546,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2058886633</t>
+          <t>11679515</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058886633</t>
+          <t>https://m.place.naver.com/place/11679515</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3564,48 +3568,44 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>원주국제걷기대회</t>
+          <t>HM 휘트니스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mmsus2392@naver.com</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>kwf@walking.kr</t>
-        </is>
-      </c>
+          <t>hm_7777@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>033-762-2234</t>
+          <t>0507-1392-5874</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 단구로 170 원주따뚜공연장</t>
+          <t>강원특별자치도 원주시 서원대로 396 2층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://www.koreawalk.kr/</t>
+          <t>https://blog.naver.com/hm_7777</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3621,17 +3621,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="Q34" t="n">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="R34" t="n">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3640,12 +3640,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>13045168</t>
+          <t>51291896</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13045168</t>
+          <t>https://m.place.naver.com/place/51291896</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3662,29 +3662,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HM 휘트니스</t>
+          <t>스카이짐</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>hm_7777@naver.com</t>
+          <t>seee9518@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1392-5874</t>
+          <t>033-746-6080</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 서원대로 396 2층</t>
+          <t>강원특별자치도 원주시 남산로 180 8층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hm_7777</t>
+          <t>https://blog.naver.com/seee9518</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3719,13 +3719,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>119</v>
+        <v>9</v>
       </c>
       <c r="R35" t="n">
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>51291896</t>
+          <t>1340553997</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/51291896</t>
+          <t>https://m.place.naver.com/place/1340553997</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3756,29 +3756,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>몬스터짐 요가&amp;PT헬스</t>
+          <t>제이엠피트니스</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>chlwlgns6138@naver.com</t>
+          <t>deny7004@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1474-3328</t>
+          <t>033-733-3336</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 건강로 23 4층</t>
+          <t>강원특별자치도 원주시 건강로 17 스타타워2. 5층 502호 503호 504호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chlwlgns6138</t>
+          <t>https://blog.naver.com/deny7004</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3809,17 +3809,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R36" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3828,12 +3828,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2041484449</t>
+          <t>2005941753</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2041484449</t>
+          <t>https://m.place.naver.com/place/2005941753</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3944,29 +3944,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>훈짐 원주점</t>
+          <t>무실동 듀플릿 헬스/PT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>hoongym@naver.com</t>
+          <t>jin10240107@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>033-766-8221</t>
+          <t>0507-1306-6059</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 흥업면 남원로 52-5 1층, 2층</t>
+          <t>강원특별자치도 원주시 능라동길 70 5층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hoongym</t>
+          <t>https://blog.naver.com/jin10240107</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>57</v>
+        <v>3506</v>
       </c>
       <c r="Q38" t="n">
-        <v>216</v>
+        <v>740</v>
       </c>
       <c r="R38" t="n">
-        <v>273</v>
+        <v>4246</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4016,12 +4016,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1943954995</t>
+          <t>1659772512</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1943954995</t>
+          <t>https://m.place.naver.com/place/1659772512</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4038,29 +4038,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>히든헬스클럽</t>
+          <t>블루짐</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jayttt@naver.com</t>
+          <t>bluegym_2412@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>033-762-1120</t>
+          <t>0507-1443-7200</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 무실로 189 2층</t>
+          <t>강원특별자치도 원주시 백간길 55 101-4호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jayttt</t>
+          <t>https://blog.naver.com/bluegym_2412</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4110,12 +4110,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>38278726</t>
+          <t>1335716320</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38278726</t>
+          <t>https://m.place.naver.com/place/1335716320</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4127,34 +4127,34 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>크로스핏에임 혁신점</t>
+          <t>블랑꼬 PT&amp;헬스 태장점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tafjq1004@naver.com</t>
+          <t>dlarhkddbf1@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1319-5745</t>
+          <t>0507-1330-4023</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 혁신로 39-2 1층 107호, 108호</t>
+          <t>강원특별자치도 원주시 흥양로18번길 35 . 지하 1층&amp;2층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dlarhkddbf1</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4180,22 +4180,22 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="Q40" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="R40" t="n">
-        <v>7</v>
+        <v>143</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1853505932</t>
+          <t>1901538636</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853505932</t>
+          <t>https://m.place.naver.com/place/1901538636</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4226,24 +4226,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>유진헬스클럽</t>
+          <t>골드휘트니스 문막점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>insightmedia@naver.com</t>
+          <t>gustn7373@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>033-761-5959</t>
+          <t>0507-1363-2070</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 황소마을길 40</t>
+          <t>강원특별자치도 원주시 문막읍 왕건로 46</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4283,13 +4283,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4298,12 +4298,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>11679515</t>
+          <t>15256122</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11679515</t>
+          <t>https://m.place.naver.com/place/15256122</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4320,24 +4320,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>헬스붐</t>
+          <t>비타민헬스클럽</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>wkdwnel4@naver.com</t>
+          <t>shichichi@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>033-734-9061</t>
+          <t>033-746-7494</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 흥양로51번길 108</t>
+          <t>강원특별자치도 원주시 흥양로18번길 33</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4377,13 +4377,13 @@
         </is>
       </c>
       <c r="P42" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q42" t="n">
         <v>16</v>
       </c>
-      <c r="Q42" t="n">
-        <v>2</v>
-      </c>
       <c r="R42" t="n">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4392,12 +4392,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>15282839</t>
+          <t>15282842</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15282839</t>
+          <t>https://m.place.naver.com/place/15282842</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4414,29 +4414,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>엠투짐</t>
+          <t>에이스스포츠센터&amp;에이스짐PT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>k1140391@naver.com</t>
+          <t>jth3824@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1358-1467</t>
+          <t>0507-1336-5769</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 혁신로 39-2 서울메디컬센터 5층</t>
+          <t>강원특별자치도 원주시 원일로115번길 16 4층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/m2gym.spinning</t>
+          <t>https://www.instagram.com/acegym_wonju</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4471,13 +4471,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>179</v>
+        <v>1583</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>919</v>
       </c>
       <c r="R43" t="n">
-        <v>207</v>
+        <v>2502</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>37912788</t>
+          <t>15201329</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37912788</t>
+          <t>https://m.place.naver.com/place/15201329</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4503,34 +4503,34 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>비브레 PT/헬스 혁신점</t>
+          <t>엑스스피닝</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>wonju_ht@naver.com</t>
+          <t>spinning1004@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1354-8955</t>
+          <t>0507-1361-2234</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원특별자치도 원주시 능라동길 51 시네시티타워 6층 619호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://vivre-training.com/</t>
+          <t>https://blog.naver.com/spinning1004</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4561,17 +4561,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>378</v>
+        <v>23</v>
       </c>
       <c r="Q44" t="n">
-        <v>2178</v>
+        <v>38</v>
       </c>
       <c r="R44" t="n">
-        <v>2556</v>
+        <v>61</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1193233179</t>
+          <t>1195598010</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193233179</t>
+          <t>https://m.place.naver.com/place/1195598010</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4602,29 +4602,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>반곡뮤직스피닝</t>
+          <t>상아휘트니스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>zkscy293@naver.com</t>
+          <t>ablegym9@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1335-4279</t>
+          <t>033-747-6398</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 늘품로 187-58 현대아카데미 5층 뮤직스피닝</t>
+          <t>강원특별자치도 원주시 바우골길 8 프렌티어스빌딩5층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/musicspinning_bangok?igsh=MW55NGxzaHFrZG4yZw%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4655,17 +4655,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="R45" t="n">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1766314585</t>
+          <t>15214867</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1766314585</t>
+          <t>https://m.place.naver.com/place/15214867</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4696,29 +4696,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ROAD GYM</t>
+          <t>크로스핏에임 혁신점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ghsk52@naver.com</t>
+          <t>tafjq1004@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>033-743-6766</t>
+          <t>0507-1319-5745</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 시청로 80 쎈터프라자 10층</t>
+          <t>강원특별자치도 원주시 혁신로 39-2 1층 107호, 108호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ghsk52</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4749,17 +4749,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="R46" t="n">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4768,12 +4768,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>15247473</t>
+          <t>1853505932</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15247473</t>
+          <t>https://m.place.naver.com/place/1853505932</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4790,29 +4790,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>커브스 무실클럽</t>
+          <t>리온 휘트니스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sputnik23@naver.com</t>
+          <t>reon_fitness1@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>033-742-7330</t>
+          <t>0507-1369-8925</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 시청로 80 쎈터프라자 3층</t>
+          <t>강원특별자치도 원주시 문막읍 왕건로 81 3층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sputnik23</t>
+          <t>https://blog.naver.com/reon_fitness1</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>54</v>
+        <v>225</v>
       </c>
       <c r="Q47" t="n">
-        <v>9</v>
+        <v>167</v>
       </c>
       <c r="R47" t="n">
-        <v>63</v>
+        <v>392</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4862,12 +4862,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>36538620</t>
+          <t>1876515774</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36538620</t>
+          <t>https://m.place.naver.com/place/1876515774</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4884,39 +4884,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>스타트라인 혁신점</t>
+          <t>저스트포짐</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>startupkised@naver.com</t>
+          <t>24hourfitness@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1344-3599</t>
+          <t>0507-1472-1476</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 웅비1길 12-1 1층</t>
+          <t>강원특별자치도 원주시 황금로 20 404호 저스트포짐</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/origin_wan?igsh=ajJwN201dXJham9p</t>
+          <t>https://booking.naver.com/booking/13/bizes/1409591</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4941,13 +4941,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="R48" t="n">
-        <v>4</v>
+        <v>209</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1296426839</t>
+          <t>1943100672</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296426839</t>
+          <t>https://m.place.naver.com/place/1943100672</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -4978,34 +4978,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>비타민헬스클럽</t>
+          <t>원주국제걷기대회</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>shichichi@naver.com</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>mmsus2392@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>kwf@walking.kr</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>033-746-7494</t>
+          <t>033-762-2234</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 흥양로18번길 33</t>
+          <t>강원특별자치도 원주시 단구로 170 원주따뚜공연장</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.koreawalk.kr/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5031,17 +5035,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="Q49" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R49" t="n">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5050,12 +5054,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>15282842</t>
+          <t>13045168</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15282842</t>
+          <t>https://m.place.naver.com/place/13045168</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5072,25 +5076,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>비엔케이피트니스클럽</t>
+          <t>호크아이짐 헬스/PT/태닝</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>flavorhunter_@naver.com</t>
+          <t>hawkeyegym@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1307-5822</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 나비허리길 97</t>
+          <t>강원특별자치도 원주시 서원대로 106 3층 호크아이짐</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/hawkeyegym</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5100,12 +5108,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5116,22 +5124,22 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>4207</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>5022</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5140,12 +5148,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1797081807</t>
+          <t>1602901180</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1797081807</t>
+          <t>https://m.place.naver.com/place/1602901180</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5162,29 +5170,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>하디웨이트짐</t>
+          <t>반곡뮤직스피닝</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>hardyweightgym@naver.com</t>
+          <t>zkscy293@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1334-8501</t>
+          <t>0507-1335-4279</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 천사로 178 지하1층</t>
+          <t>강원특별자치도 원주시 늘품로 187-58 현대아카데미 5층 뮤직스피닝</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hardyweightgym</t>
+          <t>https://www.instagram.com/musicspinning_bangok?igsh=MW55NGxzaHFrZG4yZw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5199,7 +5207,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5215,17 +5223,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5234,12 +5242,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2034880654</t>
+          <t>1766314585</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2034880654</t>
+          <t>https://m.place.naver.com/place/1766314585</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5251,34 +5259,34 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>목욕탕,사우나</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>더바른PT / 헬스 혁신점</t>
+          <t>청담사우나헬스</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>thebarnnpt@naver.com</t>
+          <t>ohkfifa@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1491-1113</t>
+          <t>0507-1482-1126</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 혁신로 53 4층 더바른PT</t>
+          <t>강원특별자치도 원주시 남원로534번길 64</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thebarnnpt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5288,12 +5296,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5304,22 +5312,22 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>179</v>
+        <v>321</v>
       </c>
       <c r="Q52" t="n">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="R52" t="n">
-        <v>421</v>
+        <v>350</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5328,12 +5336,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1850025502</t>
+          <t>1245074192</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850025502</t>
+          <t>https://m.place.naver.com/place/1245074192</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5350,29 +5358,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>원주인터불고 웰니스센터</t>
+          <t>크로스핏 컴뱃</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>yjw5443@naver.com</t>
+          <t>taiwansister@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>033-769-8201</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 동부순환로 200</t>
+          <t>강원특별자치도 원주시 만대공원길 64 1층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/crossfit__combat</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5382,7 +5386,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5403,17 +5407,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="R53" t="n">
-        <v>83</v>
+        <v>210</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5422,12 +5426,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1339846931</t>
+          <t>36369149</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1339846931</t>
+          <t>https://m.place.naver.com/place/36369149</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5444,29 +5448,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>리온 휘트니스</t>
+          <t>히든헬스클럽</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>reon_fitness1@naver.com</t>
+          <t>jayttt@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1369-8925</t>
+          <t>033-762-1120</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 문막읍 왕건로 81 3층</t>
+          <t>강원특별자치도 원주시 무실로 189 2층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/reon_fitness1</t>
+          <t>https://blog.naver.com/jayttt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5497,17 +5501,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>225</v>
+        <v>24</v>
       </c>
       <c r="Q54" t="n">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="R54" t="n">
-        <v>392</v>
+        <v>124</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5516,12 +5520,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1876515774</t>
+          <t>38278726</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1876515774</t>
+          <t>https://m.place.naver.com/place/38278726</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5533,34 +5537,34 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>바디라인휘트니스 원주무실점</t>
+          <t>펄핏 스튜디오 PT/헬스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>bodyline2@naver.com</t>
+          <t>gomete6363@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1428-3415</t>
+          <t>0507-1389-9039</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
+          <t>강원특별자치도 원주시 천매봉길 32-22 2층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline2</t>
+          <t>https://www.instagram.com/pearl_fit_</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5575,7 +5579,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5595,13 +5599,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>717</v>
+        <v>124</v>
       </c>
       <c r="Q55" t="n">
-        <v>727</v>
+        <v>368</v>
       </c>
       <c r="R55" t="n">
-        <v>1444</v>
+        <v>492</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5610,12 +5614,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1140023595</t>
+          <t>1471872878</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140023595</t>
+          <t>https://m.place.naver.com/place/1471872878</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5632,29 +5636,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>오짐 헬스&amp;PT</t>
+          <t>블랑꼬 PT&amp;헬스 기업도시점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>wonjuogym@naver.com</t>
+          <t>dlarhkddbf1@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1406-2506</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 모란1길 69 3층</t>
+          <t>강원특별자치도 원주시 지정면 신지정로 316-1 4층(골드파크빌딩)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wonjuogym</t>
+          <t>https://blog.naver.com/dlarhkddbf1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5689,13 +5689,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>4009</v>
+        <v>269</v>
       </c>
       <c r="Q56" t="n">
-        <v>364</v>
+        <v>165</v>
       </c>
       <c r="R56" t="n">
-        <v>4373</v>
+        <v>434</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5704,12 +5704,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1101731614</t>
+          <t>1401069241</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1101731614</t>
+          <t>https://m.place.naver.com/place/1401069241</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5726,29 +5726,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>엔터핏헬스&amp;골프</t>
+          <t>커브스 단구클럽</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>enterfit_wonju@naver.com</t>
+          <t>weonju007@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1424-8254</t>
+          <t>0507-1447-4030</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 입춘로 69 4층 401호</t>
+          <t>강원특별자치도 원주시 서원대로 392 스타프라자 3층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/enterfit_wonju/223823197126</t>
+          <t>https://www.instagram.com/curvesdangu_</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5783,13 +5783,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="Q57" t="n">
-        <v>279</v>
+        <v>16</v>
       </c>
       <c r="R57" t="n">
-        <v>335</v>
+        <v>69</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5798,12 +5798,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1866503944</t>
+          <t>21547560</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1866503944</t>
+          <t>https://m.place.naver.com/place/21547560</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5820,29 +5820,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>무실동 듀플릿 헬스/PT</t>
+          <t>크로스핏BK 혁신점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jin10240107@naver.com</t>
+          <t>thlqhd00@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1306-6059</t>
+          <t>0507-1439-2177</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 70 5층</t>
+          <t>강원특별자치도 원주시 웅비2길 10 봉우빌딩 B1층 크로스핏BK</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jin10240107</t>
+          <t>https://blog.naver.com/thlqhd00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5877,13 +5877,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3507</v>
+        <v>55</v>
       </c>
       <c r="Q58" t="n">
-        <v>740</v>
+        <v>123</v>
       </c>
       <c r="R58" t="n">
-        <v>4247</v>
+        <v>178</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5892,12 +5892,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1659772512</t>
+          <t>1074040282</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659772512</t>
+          <t>https://m.place.naver.com/place/1074040282</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5909,34 +5909,34 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>점핑스피닝GX</t>
+          <t>노익스짐 PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>dessing34@naver.com</t>
+          <t>no_x_gym@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>033-813-0051</t>
+          <t>0507-1486-6692</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 반곡초교로 77-2</t>
+          <t>강원특별자치도 원주시 무실본동길 38 1층 노익스짐</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/no_x_gym</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5967,17 +5967,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>6</v>
+        <v>287</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>864</v>
       </c>
       <c r="R59" t="n">
-        <v>11</v>
+        <v>1151</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5986,12 +5986,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1972135147</t>
+          <t>1213015794</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1972135147</t>
+          <t>https://m.place.naver.com/place/1213015794</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6008,29 +6008,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>블랑꼬 PT&amp;헬스 태장점</t>
+          <t>바디아카데미 PT 프리미엄센터</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>dlarhkddbf1@naver.com</t>
+          <t>dlrlckdtkdwl@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1330-4023</t>
+          <t>033-900-7450</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 흥양로18번길 35 . 지하 1층&amp;2층</t>
+          <t>강원특별자치도 원주시 능라동길 34-1 센트럴프라자 3차 3층 바디아카데미 PT 프리미엄센터</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlarhkddbf1</t>
+          <t>https://www.instagram.com/ki_chang_l/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6056,7 +6056,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6065,13 +6065,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q60" t="n">
-        <v>59</v>
+        <v>593</v>
       </c>
       <c r="R60" t="n">
-        <v>143</v>
+        <v>680</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1901538636</t>
+          <t>1329553206</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1901538636</t>
+          <t>https://m.place.naver.com/place/1329553206</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6097,34 +6097,34 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>엑스스피닝</t>
+          <t>헤이스바디랩</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>spinning1004@naver.com</t>
+          <t>heisbodylab@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1361-2234</t>
+          <t>0506-571-3069</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 51 시네시티타워 6층 619호</t>
+          <t>강원특별자치도 원주시 흥양로51번길 1 원마트 2층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spinning1004</t>
+          <t>https://www.instagram.com/heis_body_lab</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6155,17 +6155,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="Q61" t="n">
-        <v>38</v>
+        <v>205</v>
       </c>
       <c r="R61" t="n">
-        <v>61</v>
+        <v>211</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6174,12 +6174,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1195598010</t>
+          <t>1399142746</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1195598010</t>
+          <t>https://m.place.naver.com/place/1399142746</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6191,34 +6191,34 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>저스트포짐</t>
+          <t>핏앤피트니스 혁신점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>24hourfitness@naver.com</t>
+          <t>ssb154911@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1472-1476</t>
+          <t>033-735-0302</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 황금로 20 404호 저스트포짐</t>
+          <t>강원특별자치도 원주시 미래로 1 강림빌딩 3층 302호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/1409591</t>
+          <t>https://fitandfitness.imweb.me</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6253,13 +6253,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="Q62" t="n">
-        <v>182</v>
+        <v>284</v>
       </c>
       <c r="R62" t="n">
-        <v>209</v>
+        <v>406</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1943100672</t>
+          <t>1042681042</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1943100672</t>
+          <t>https://m.place.naver.com/place/1042681042</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6285,34 +6285,30 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>대동헬스피아</t>
+          <t>엑스바디 PT 스튜디오 무실동</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>onsi09@naver.com</t>
+          <t>xbody1101@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>033-748-3279</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 북원상가길 13 북원상가 3층</t>
+          <t>강원특별자치도 원주시 시청로 86 부영골든빌 4층 403호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://ok114.co.kr/0337483279</t>
+          <t>https://www.instagram.com/x.body_ptstudio</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6322,7 +6318,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6343,17 +6339,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>6</v>
+        <v>116</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>316</v>
       </c>
       <c r="R63" t="n">
-        <v>12</v>
+        <v>432</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6362,12 +6358,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>15282840</t>
+          <t>1571856002</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15282840</t>
+          <t>https://m.place.naver.com/place/1571856002</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6379,34 +6375,34 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>월드헬스휘트니스</t>
+          <t>클래식짐 PT 혁신점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>yun3392@naver.com</t>
+          <t>classicgym2749@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>033-746-9977</t>
+          <t>0507-1313-2749</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 문막읍 왕건로 22</t>
+          <t>강원특별자치도 원주시 황금로 20 5층 502호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/classicgym2749</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6416,12 +6412,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6437,17 +6433,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6456,12 +6452,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>19928385</t>
+          <t>1324878145</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19928385</t>
+          <t>https://m.place.naver.com/place/1324878145</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6473,34 +6469,34 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>메가짐 PT&amp;필라테스</t>
+          <t>바디아카데미 혁신도시점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>megagym9932@naver.com</t>
+          <t>wkdgusxo12345@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1325-9932</t>
+          <t>0507-1493-4412</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 서원대로 165-3 아트스페이스 5층</t>
+          <t>강원특별자치도 원주시 양지로 20 오썸파크 209호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/megagym9932</t>
+          <t>https://www.instagram.com/body___academy_ht</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6515,7 +6511,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6535,13 +6531,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1726</v>
+        <v>68</v>
       </c>
       <c r="Q65" t="n">
-        <v>336</v>
+        <v>86</v>
       </c>
       <c r="R65" t="n">
-        <v>2062</v>
+        <v>154</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6550,12 +6546,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1302676152</t>
+          <t>1128838469</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302676152</t>
+          <t>https://m.place.naver.com/place/1128838469</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6666,34 +6662,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>피지컬짐</t>
+          <t>조거앤스웨트</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>physicalgym03@naver.com</t>
+          <t>woonduong@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1422-6460</t>
+          <t>0507-1447-9913</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 혁신로 37-1 반곡빌딩 3층 301호</t>
+          <t>강원특별자치도 원주시 혁신로 35 202호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/physicalgym03</t>
+          <t>https://www.instagram.com/jogger_sweat</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6703,7 +6699,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6723,13 +6719,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="R67" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6738,12 +6734,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1324996335</t>
+          <t>1412402393</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324996335</t>
+          <t>https://m.place.naver.com/place/1412402393</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6760,29 +6756,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>핏앤피트니스 PT &amp; 그룹피티 기업점</t>
+          <t>혁신런앤핏</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>rlghks405@naver.com</t>
+          <t>hghghghg00@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1328-0301</t>
+          <t>0507-1346-7262</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 지정면 신지정로 172 6층</t>
+          <t>강원특별자치도 원주시 혁신로 19 지하층 101호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlghks405</t>
+          <t>https://www.instagram.com/hs_run_fit</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6797,7 +6793,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6817,13 +6813,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>292</v>
+        <v>23</v>
       </c>
       <c r="R68" t="n">
-        <v>395</v>
+        <v>23</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6832,12 +6828,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1139721387</t>
+          <t>1223719800</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1139721387</t>
+          <t>https://m.place.naver.com/place/1223719800</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6854,24 +6850,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>다이아짐</t>
+          <t>컨피던스짐 원주 단계점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>top-health@naver.com</t>
+          <t>heyoungshin@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1428-5618</t>
+          <t>0507-1444-9680</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 37 302호</t>
+          <t>강원특별자치도 원주시 단구로 80 1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6911,13 +6907,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q69" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6926,12 +6922,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1877473254</t>
+          <t>1341284821</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877473254</t>
+          <t>https://m.place.naver.com/place/1341284821</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6948,44 +6944,44 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OK시니어체인지클럽</t>
+          <t>핏앤피트니스 PT &amp; 그룹피티</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>okscc-@naver.com</t>
+          <t>ssz1549@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1481-0006</t>
+          <t>0507-1445-0383</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 서원대로 402 4층 402호</t>
+          <t>강원특별자치도 원주시 능라동길 47 8층,핏앤피트니스</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://연세오케이정형외과.kr/ok-change-club</t>
+          <t>https://www.youtube.com/@hipupschool</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6996,7 +6992,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7005,13 +7001,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>11</v>
+        <v>238</v>
       </c>
       <c r="Q70" t="n">
-        <v>77</v>
+        <v>778</v>
       </c>
       <c r="R70" t="n">
-        <v>88</v>
+        <v>1016</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7020,12 +7016,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2086283255</t>
+          <t>1793276177</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086283255</t>
+          <t>https://m.place.naver.com/place/1793276177</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7042,29 +7038,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>바디아카데미 PT 프리미엄센터</t>
+          <t>바디아카데미 기업도시점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>dlrlckdtkdwl@naver.com</t>
+          <t>juseokchan91@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>033-900-7450</t>
+          <t>0507-1393-4411</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 34-1 센트럴프라자 3차 3층 바디아카데미 PT 프리미엄센터</t>
+          <t>강원특별자치도 원주시 지정면 신지정로 212 롯데퍼스트프라자 6층 바디아카데미</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ki_chang_l/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7074,7 +7070,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7095,17 +7091,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="Q71" t="n">
-        <v>593</v>
+        <v>146</v>
       </c>
       <c r="R71" t="n">
-        <v>680</v>
+        <v>152</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7114,12 +7110,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1329553206</t>
+          <t>1896388555</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1329553206</t>
+          <t>https://m.place.naver.com/place/1896388555</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7136,29 +7132,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>바디아카데미 기업도시점</t>
+          <t>리햅포먼스</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>juseokchan91@naver.com</t>
+          <t>rehabformance@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1393-4411</t>
+          <t>0507-1324-4662</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 지정면 신지정로 212 롯데퍼스트프라자 6층 바디아카데미</t>
+          <t>강원특별자치도 원주시 만대로 166 4층 리햅포먼스</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rehabformance</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7168,12 +7164,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7189,17 +7185,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="Q72" t="n">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="R72" t="n">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7208,12 +7204,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1896388555</t>
+          <t>1229524729</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1896388555</t>
+          <t>https://m.place.naver.com/place/1229524729</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7230,25 +7226,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>비브레 프리미엄점 PT &amp; 필라테스</t>
+          <t>OK시니어체인지클럽</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>wonju_ht@naver.com</t>
+          <t>okscc-@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1481-0006</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 건강로 17-2 5층 ( 501~502호)</t>
+          <t>강원특별자치도 원주시 서원대로 402 4층 402호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://vivre-training.com/</t>
+          <t>https://연세오케이정형외과.kr/ok-change-club</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7274,7 +7274,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>284</v>
+        <v>11</v>
       </c>
       <c r="Q73" t="n">
-        <v>627</v>
+        <v>77</v>
       </c>
       <c r="R73" t="n">
-        <v>911</v>
+        <v>88</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7298,12 +7298,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1370848344</t>
+          <t>2086283255</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1370848344</t>
+          <t>https://m.place.naver.com/place/2086283255</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7320,34 +7320,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>핏앤피트니스 혁신점</t>
+          <t>몸수선토탈케어PT샵</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ssb154911@naver.com</t>
+          <t>dmsal04@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>033-735-0302</t>
+          <t>0507-1423-0830</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 미래로 1 강림빌딩 3층 302호</t>
+          <t>강원특별자치도 원주시 천매봉길 58 1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://fitandfitness.imweb.me</t>
+          <t>https://www.instagram.com/momsuseon?igsh=d3NiM3MwNTYzaXA4</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>284</v>
+        <v>37</v>
       </c>
       <c r="R74" t="n">
-        <v>406</v>
+        <v>37</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7392,12 +7392,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1042681042</t>
+          <t>1964597317</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1042681042</t>
+          <t>https://m.place.naver.com/place/1964597317</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7414,29 +7414,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>본움 체형교정 선수트레이닝 센터</t>
+          <t>비플로우PT&amp;그룹PT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>rlghks00235@naver.com</t>
+          <t>bflowpt@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1336-1466</t>
+          <t>0507-1437-1576</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 미래로 1 3층 303호</t>
+          <t>강원특별자치도 원주시 능라동길 9 3층 비플로우</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlghks00235</t>
+          <t>https://blog.naver.com/bflowpt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7467,17 +7467,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="Q75" t="n">
-        <v>48</v>
+        <v>664</v>
       </c>
       <c r="R75" t="n">
-        <v>56</v>
+        <v>899</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7486,12 +7486,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>2088505203</t>
+          <t>1870827414</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2088505203</t>
+          <t>https://m.place.naver.com/place/1870827414</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7508,29 +7508,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>핏앤피트니스 PT &amp; 그룹피티</t>
+          <t>핏앤피트니스 PT &amp; 그룹피티 기업점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ssz1549@naver.com</t>
+          <t>rlghks405@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1445-0383</t>
+          <t>0507-1328-0301</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 47 8층,핏앤피트니스</t>
+          <t>강원특별자치도 원주시 지정면 신지정로 172 6층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@hipupschool</t>
+          <t>https://blog.naver.com/rlghks405</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7565,13 +7565,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>238</v>
+        <v>103</v>
       </c>
       <c r="Q76" t="n">
-        <v>778</v>
+        <v>292</v>
       </c>
       <c r="R76" t="n">
-        <v>1016</v>
+        <v>395</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1793276177</t>
+          <t>1139721387</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1793276177</t>
+          <t>https://m.place.naver.com/place/1139721387</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7602,25 +7602,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>엑스바디 PT 스튜디오 무실동</t>
+          <t>본움 체형교정 선수트레이닝 센터</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>xbody1101@naver.com</t>
+          <t>rlghks00235@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1336-1466</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 시청로 86 부영골든빌 4층 403호</t>
+          <t>강원특별자치도 원주시 미래로 1 3층 303호</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/x.body_ptstudio</t>
+          <t>https://blog.naver.com/rlghks00235</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7635,7 +7639,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -7651,17 +7655,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="Q77" t="n">
-        <v>316</v>
+        <v>48</v>
       </c>
       <c r="R77" t="n">
-        <v>432</v>
+        <v>56</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7670,12 +7674,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1571856002</t>
+          <t>2088505203</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1571856002</t>
+          <t>https://m.place.naver.com/place/2088505203</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7692,29 +7696,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>몸수선토탈케어PT샵</t>
+          <t>율핏피트니스 PT센터 무실점</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>dmsal04@naver.com</t>
+          <t>yulgym@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>0507-1423-0830</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 천매봉길 58 1층</t>
+          <t>강원특별자치도 원주시 능라동길 65 휴먼타워 9층 902호 903호 (무실동 1857-1)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/momsuseon?igsh=d3NiM3MwNTYzaXA4</t>
+          <t>https://blog.naver.com/yulgym</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7749,13 +7749,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="Q78" t="n">
-        <v>37</v>
+        <v>522</v>
       </c>
       <c r="R78" t="n">
-        <v>37</v>
+        <v>1008</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7764,12 +7764,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1964597317</t>
+          <t>481098140</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1964597317</t>
+          <t>https://m.place.naver.com/place/481098140</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7786,29 +7786,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>네츄럴 올림피아</t>
+          <t>컨피던스짐 단구점</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ojg4205@naver.com</t>
+          <t>confidencegym@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>033-732-0035</t>
+          <t>0507-1348-9679</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 시청로 160-1 노블인갤러리 2F (법원맞은편)</t>
+          <t>강원특별자치도 원주시 남원로534번길 51 2층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/confidence_1st</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7839,17 +7839,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="Q79" t="n">
-        <v>3</v>
+        <v>319</v>
       </c>
       <c r="R79" t="n">
-        <v>6</v>
+        <v>439</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7858,12 +7858,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>31674353</t>
+          <t>1250040920</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31674353</t>
+          <t>https://m.place.naver.com/place/1250040920</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7875,39 +7875,35 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내체육관</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>혁신런앤핏</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>hghghghg00@naver.com</t>
-        </is>
-      </c>
+          <t>원주시농민문화체육센터</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1346-7262</t>
+          <t>033-737-4725</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 혁신로 19 지하층 101호</t>
+          <t>강원특별자치도 원주시 문막읍 건등로 21 농민문화체육센터</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hs_run_fit</t>
+          <t>https://yeyak.wonju.go.kr/www/main.do</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7933,17 +7929,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="Q80" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="R80" t="n">
-        <v>23</v>
+        <v>174</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7952,12 +7948,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1223719800</t>
+          <t>21387721</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223719800</t>
+          <t>https://m.place.naver.com/place/21387721</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7969,35 +7965,39 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내체육관</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>율핏피트니스 PT센터 무실점</t>
+          <t>원주남부 복합체육센터</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>yulgym@naver.com</t>
+          <t>wjkk87@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>033-737-4955</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 능라동길 65 휴먼타워 9층 902호 903호 (무실동 1857-1)</t>
+          <t>강원특별자치도 원주시 이화5길 70</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yulgym</t>
+          <t>https://www.wonju.go.kr/www/contents.do?key=6028&amp;</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8018,7 +8018,7 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -8027,13 +8027,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>486</v>
+        <v>28</v>
       </c>
       <c r="Q81" t="n">
-        <v>522</v>
+        <v>83</v>
       </c>
       <c r="R81" t="n">
-        <v>1008</v>
+        <v>111</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8042,12 +8042,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>481098140</t>
+          <t>1282336869</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/481098140</t>
+          <t>https://m.place.naver.com/place/1282336869</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8059,39 +8059,39 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내체육관</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>리햅포먼스</t>
+          <t>원주드림체육관</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>rehabformance@naver.com</t>
+          <t>anaber@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1324-4662</t>
+          <t>033-737-4666</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>강원특별자치도 원주시 만대로 166 4층 리햅포먼스</t>
+          <t>강원특별자치도 원주시 현충로 53-1 원주드림체육관</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rehabformance</t>
+          <t>https://www.wonju.go.kr/facility/contents.do?key=6385&amp;</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8117,17 +8117,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Q82" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="R82" t="n">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8136,1695 +8136,15 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1229524729</t>
+          <t>34605311</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229524729</t>
+          <t>https://m.place.naver.com/place/34605311</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>컨피던스짐 단구점</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>confidencegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0507-1348-9679</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 남원로534번길 51 2층</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/confidence_1st</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P83" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>319</v>
-      </c>
-      <c r="R83" t="n">
-        <v>439</v>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>1250040920</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1250040920</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>바디아카데미 혁신도시점</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>wkdgusxo12345@naver.com</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>0507-1493-4412</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 양지로 20 오썸파크 209호</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/body___academy_ht</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P84" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>86</v>
-      </c>
-      <c r="R84" t="n">
-        <v>154</v>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>1128838469</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1128838469</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>조거앤스웨트</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>woonduong@naver.com</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>0507-1447-9913</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 혁신로 35 202호</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jogger_sweat</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P85" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>16</v>
-      </c>
-      <c r="R85" t="n">
-        <v>28</v>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>1412402393</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1412402393</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>원주무실동프리미엄피티</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>h__a843@naver.com</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 로아노크로 76 1층</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P86" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>3</v>
-      </c>
-      <c r="R86" t="n">
-        <v>18</v>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>1217507491</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1217507491</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>헤이스바디랩</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>heisbodylab@naver.com</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>0506-571-3069</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 흥양로51번길 1 원마트 2층</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/heis_body_lab</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P87" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>205</v>
-      </c>
-      <c r="R87" t="n">
-        <v>211</v>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>1399142746</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1399142746</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>스노블트레이닝PT센터</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>igtrainer@naver.com</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>0507-1349-8857</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 황금로 29 4층 401호</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/@youreyelevel</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P88" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>88</v>
-      </c>
-      <c r="R88" t="n">
-        <v>110</v>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>2028571477</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2028571477</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>컨피던스짐 원주 단계점</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>heyoungshin@naver.com</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0507-1444-9680</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 단구로 80 1층</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P89" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>29</v>
-      </c>
-      <c r="R89" t="n">
-        <v>53</v>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>1341284821</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1341284821</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>바디팩토리웰니스짐</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>rntjdah2@naver.com</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 만대로 158</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/rntjdah2</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>55</v>
-      </c>
-      <c r="R90" t="n">
-        <v>55</v>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>35958713</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/35958713</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>클래식짐 PT 혁신점</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>classicgym2749@naver.com</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>0507-1313-2749</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 황금로 20 5층 502호</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/classicgym2749</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P91" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>84</v>
-      </c>
-      <c r="R91" t="n">
-        <v>160</v>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>1324878145</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1324878145</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>다르짐</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>lozebons@naver.com</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>0507-1358-9021</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 섬밭들1길 26-9 1층 다르짐</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/runner_dar/</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P92" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>2</v>
-      </c>
-      <c r="R92" t="n">
-        <v>6</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>1344578636</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1344578636</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>비플로우PT&amp;그룹PT</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>bflowpt@naver.com</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>0507-1437-1576</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 능라동길 9 3층 비플로우</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/bflowpt</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P93" t="n">
-        <v>235</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>664</v>
-      </c>
-      <c r="R93" t="n">
-        <v>899</v>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>1870827414</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1870827414</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>앤비 프라이빗 짐</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>johnkhong13@naver.com</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>033-732-5777</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 건강로 25 서영 에비뉴파크 1차 602호</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/johnkhong13</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P94" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>13</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>37676393</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/37676393</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>노익스짐 PT</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>no_x_gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>0507-1486-6692</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 무실본동길 38 1층 노익스짐</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/no_x_gym</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P95" t="n">
-        <v>287</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>864</v>
-      </c>
-      <c r="R95" t="n">
-        <v>1151</v>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>1213015794</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1213015794</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>실내체육관</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>원주시농민문화체육센터</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>033-737-4725</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 문막읍 건등로 21 농민문화체육센터</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>https://yeyak.wonju.go.kr/www/main.do</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P96" t="n">
-        <v>126</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>48</v>
-      </c>
-      <c r="R96" t="n">
-        <v>174</v>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>21387721</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/21387721</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>실내체육관</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>원주남부 복합체육센터</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>wjkk87@naver.com</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>033-737-4955</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 이화5길 70</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>https://www.wonju.go.kr/www/contents.do?key=6028&amp;</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P97" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>83</v>
-      </c>
-      <c r="R97" t="n">
-        <v>111</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>1282336869</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1282336869</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>실내체육관</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>원주드림체육관</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>anaber@naver.com</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>033-737-4666</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 현충로 53-1 원주드림체육관</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>https://www.wonju.go.kr/facility/contents.do?key=6385&amp;</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P98" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>43</v>
-      </c>
-      <c r="R98" t="n">
-        <v>163</v>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>34605311</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/34605311</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>요가,명상</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>지성요가원</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>wonju_jisung_yoga@naver.com</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>0507-1401-0382</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 시청로 94 보네르 빌딩 4층 지성요가원</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/jisung_yoga_wonju/</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P99" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>59</v>
-      </c>
-      <c r="R99" t="n">
-        <v>146</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>31992339</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/31992339</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>체육관</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>에임크로스핏</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>newtriple@naver.com</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>0507-1415-6004</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>강원특별자치도 원주시 북원로 1897 1층~2층</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>http://www.instagram.com/aim_crossfit</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P100" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>150</v>
-      </c>
-      <c r="R100" t="n">
-        <v>155</v>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>1062060537</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1062060537</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/원주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/원주_헬스장.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3506</v>
+        <v>3507</v>
       </c>
       <c r="Q2" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="R2" t="n">
-        <v>4246</v>
+        <v>4248</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         <v>4216</v>
       </c>
       <c r="Q3" t="n">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="R3" t="n">
-        <v>5031</v>
+        <v>5032</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="Q4" t="n">
         <v>127</v>
       </c>
       <c r="R4" t="n">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="Q5" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="R5" t="n">
         <v>1444</v>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1726</v>
+        <v>1733</v>
       </c>
       <c r="Q6" t="n">
         <v>336</v>
       </c>
       <c r="R6" t="n">
-        <v>2062</v>
+        <v>2069</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1306,10 +1306,10 @@
         <v>378</v>
       </c>
       <c r="Q9" t="n">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="R9" t="n">
-        <v>2556</v>
+        <v>2559</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/원주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/원주_헬스장.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>4216</v>
+        <v>4217</v>
       </c>
       <c r="Q3" t="n">
         <v>816</v>
       </c>
       <c r="R3" t="n">
-        <v>5032</v>
+        <v>5033</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="Q4" t="n">
         <v>127</v>
       </c>
       <c r="R4" t="n">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -922,10 +922,10 @@
         <v>716</v>
       </c>
       <c r="Q5" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="R5" t="n">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1404,10 +1404,10 @@
         <v>235</v>
       </c>
       <c r="Q10" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="R10" t="n">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/원주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/원주_헬스장.xlsx
@@ -1054,29 +1054,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>팀키스짐 &amp; PT</t>
+          <t>크로스핏 컴뱃</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>teamkis_@naver.com</t>
+          <t>masta_zero@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1399-2305</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 26 4층</t>
+          <t>강원 원주시 만대공원길 64 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamkis_</t>
+          <t>https://www.instagram.com/crossfit__combat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,19 +1087,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4olwd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2327</v>
+        <v>166</v>
       </c>
       <c r="Q7" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="R7" t="n">
-        <v>2827</v>
+        <v>210</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1433616376</t>
+          <t>36369149</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433616376</t>
+          <t>https://m.place.naver.com/place/36369149</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1147,30 +1139,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>크로스핏 컴뱃</t>
+          <t>비브레 PT\u002F헬스 혁신점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>taiwansister@naver.com</t>
+          <t>wonju_ht@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1354-8955</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 만대공원길 64 1층</t>
+          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit__combat</t>
+          <t>http://vivre-training.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1190,10 +1186,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46eja</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>166</v>
+        <v>378</v>
       </c>
       <c r="Q8" t="n">
-        <v>44</v>
+        <v>2181</v>
       </c>
       <c r="R8" t="n">
-        <v>210</v>
+        <v>2559</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36369149</t>
+          <t>1193233179</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36369149</t>
+          <t>https://m.place.naver.com/place/1193233179</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1237,34 +1237,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비브레 PT\u002F헬스 혁신점</t>
+          <t>하이컴뱃</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wonju_ht@naver.com</t>
+          <t>taiwansister@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1354-8955</t>
+          <t>0507-1347-5120</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원 원주시 송삼길 19 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://vivre-training.com/</t>
+          <t>https://www.instagram.com/hycombat__</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1284,14 +1284,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46eja</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>378</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2181</v>
+        <v>32</v>
       </c>
       <c r="R9" t="n">
-        <v>2559</v>
+        <v>37</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1193233179</t>
+          <t>2058886633</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193233179</t>
+          <t>https://m.place.naver.com/place/2058886633</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">

--- a/naver-place-crawler/results_health/원주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/원주_헬스장.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3507</v>
+        <v>3508</v>
       </c>
       <c r="Q2" t="n">
         <v>741</v>
       </c>
       <c r="R2" t="n">
-        <v>4248</v>
+        <v>4249</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>호크아이짐 헬스\u002FPT\u002F태닝</t>
+          <t>24시 피트니스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hawkeyegym@naver.com</t>
+          <t>24hourfitness_@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1307-5822</t>
+          <t>0507-1313-4048</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 원주시 서원대로 106 3층 호크아이짐</t>
+          <t>강원 원주시 서원대로 474 1, 2층 24시피트니스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hawkeyegym</t>
+          <t>https://www.instagram.com/24hoursfitness2020/?hl=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cqnu</t>
+          <t>https://talk.naver.com/ct/w4jwb5</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>4217</v>
+        <v>916</v>
       </c>
       <c r="Q3" t="n">
-        <v>816</v>
+        <v>127</v>
       </c>
       <c r="R3" t="n">
-        <v>5033</v>
+        <v>1043</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1602901180</t>
+          <t>1016379546</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1602901180</t>
+          <t>https://m.place.naver.com/place/1016379546</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24시 피트니스</t>
+          <t>호크아이짐 헬스\u002FPT\u002F태닝</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24hourfitness_@naver.com</t>
+          <t>hawkeyegym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1313-4048</t>
+          <t>0507-1307-5822</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 서원대로 474 1, 2층 24시피트니스</t>
+          <t>강원 원주시 서원대로 106 3층 호크아이짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/24hoursfitness2020/?hl=ko</t>
+          <t>https://blog.naver.com/hawkeyegym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4jwb5</t>
+          <t>https://talk.naver.com/ct/w4cqnu</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>916</v>
+        <v>4221</v>
       </c>
       <c r="Q4" t="n">
-        <v>127</v>
+        <v>816</v>
       </c>
       <c r="R4" t="n">
-        <v>1043</v>
+        <v>5037</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1016379546</t>
+          <t>1602901180</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1016379546</t>
+          <t>https://m.place.naver.com/place/1602901180</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -922,10 +922,10 @@
         <v>716</v>
       </c>
       <c r="Q5" t="n">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="R5" t="n">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1054,25 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>크로스핏 컴뱃</t>
+          <t>팀키스짐 &amp; PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>masta_zero@naver.com</t>
+          <t>teamkis_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1399-2305</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 원주시 만대공원길 64 1층</t>
+          <t>강원 원주시 능라동길 26 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit__combat</t>
+          <t>https://blog.naver.com/teamkis_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,15 +1091,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4olwd</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1107,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>166</v>
+        <v>2327</v>
       </c>
       <c r="Q7" t="n">
-        <v>44</v>
+        <v>501</v>
       </c>
       <c r="R7" t="n">
-        <v>210</v>
+        <v>2828</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36369149</t>
+          <t>1433616376</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36369149</t>
+          <t>https://m.place.naver.com/place/1433616376</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1139,34 +1147,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>비브레 PT\u002F헬스 혁신점</t>
+          <t>크로스핏 컴뱃</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wonju_ht@naver.com</t>
+          <t>masta_zero@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1354-8955</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원 원주시 만대공원길 64 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://vivre-training.com/</t>
+          <t>https://www.instagram.com/crossfit__combat</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1186,14 +1190,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46eja</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>378</v>
+        <v>166</v>
       </c>
       <c r="Q8" t="n">
-        <v>2181</v>
+        <v>44</v>
       </c>
       <c r="R8" t="n">
-        <v>2559</v>
+        <v>210</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1193233179</t>
+          <t>36369149</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193233179</t>
+          <t>https://m.place.naver.com/place/36369149</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1237,34 +1237,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>하이컴뱃</t>
+          <t>비브레 PT\u002F헬스 혁신점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>taiwansister@naver.com</t>
+          <t>wonju_ht@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1347-5120</t>
+          <t>0507-1354-8955</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 송삼길 19 1층</t>
+          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hycombat__</t>
+          <t>http://vivre-training.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1284,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46eja</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>378</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>2185</v>
       </c>
       <c r="R9" t="n">
-        <v>37</v>
+        <v>2563</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2058886633</t>
+          <t>1193233179</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058886633</t>
+          <t>https://m.place.naver.com/place/1193233179</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">

--- a/naver-place-crawler/results_health/원주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/원주_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>무실동 듀플릿 헬스\u002FPT</t>
+          <t>커브스 무실클럽</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jin10240107@naver.com</t>
+          <t>sputnik23@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1306-6059</t>
+          <t>033-742-7330</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 70 5층</t>
+          <t>강원특별자치도 원주시 시청로 80 쎈터프라자 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jin10240107</t>
+          <t>https://blog.naver.com/sputnik23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4b6cm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3509</v>
+        <v>54</v>
       </c>
       <c r="Q2" t="n">
-        <v>742</v>
+        <v>9</v>
       </c>
       <c r="R2" t="n">
-        <v>4251</v>
+        <v>63</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1659772512</t>
+          <t>36538620</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659772512</t>
+          <t>https://m.place.naver.com/place/36538620</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24시 피트니스</t>
+          <t>비엔케이피트니스클럽</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>24hourfitness_@naver.com</t>
+          <t>flavorhunter_@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1313-4048</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 원주시 서원대로 474 1, 2층 24시피트니스</t>
+          <t>강원특별자치도 원주시 나비허리길 97</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/24hoursfitness2020/?hl=ko</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +686,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,14 +696,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4jwb5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,17 +707,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1048</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1016379546</t>
+          <t>1797081807</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1016379546</t>
+          <t>https://m.place.naver.com/place/1797081807</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -760,29 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>호크아이짐 헬스\u002FPT\u002F태닝</t>
+          <t>조이클럽멀티짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hawkeyegym@naver.com</t>
+          <t>wldls1129@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1307-5822</t>
+          <t>033-766-5516</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 서원대로 106 3층 호크아이짐</t>
+          <t>강원특별자치도 원주시 나비허리길 33 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hawkeyegym</t>
+          <t>http://www.instagram.com/1joyclub</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,22 +785,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4cqnu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4224</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
-        <v>816</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
-        <v>5040</v>
+        <v>48</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1602901180</t>
+          <t>1986847768</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1602901180</t>
+          <t>https://m.place.naver.com/place/1986847768</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -858,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바디라인휘트니스 원주무실점</t>
+          <t>바이브짐 PT&amp;헬스 혁신점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bodyline2@naver.com</t>
+          <t>vibegym_@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1428-3415</t>
+          <t>0507-1490-3386</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 48-1 5층</t>
+          <t>강원특별자치도 원주시 세계로 3 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyline2</t>
+          <t>https://www.instagram.com/vibe_gym_?igsh=MXJnd2FybDBwb3F6OQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,19 +879,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4loqz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>724</v>
+        <v>120</v>
       </c>
       <c r="Q5" t="n">
-        <v>733</v>
+        <v>154</v>
       </c>
       <c r="R5" t="n">
-        <v>1457</v>
+        <v>274</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1140023595</t>
+          <t>1071680373</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140023595</t>
+          <t>https://m.place.naver.com/place/1071680373</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -956,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>메가짐 PT&amp;필라테스</t>
+          <t>오짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>megagym9932@naver.com</t>
+          <t>wonjuogym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1325-9932</t>
+          <t>0507-1406-2506</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 원주시 서원대로 165-3 아트스페이스 5층</t>
+          <t>강원특별자치도 원주시 모란1길 69 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/megagym9932</t>
+          <t>https://blog.naver.com/wonjuogym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -998,14 +978,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tavv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1735</v>
+        <v>4009</v>
       </c>
       <c r="Q6" t="n">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="R6" t="n">
-        <v>2073</v>
+        <v>4373</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1302676152</t>
+          <t>1101731614</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302676152</t>
+          <t>https://m.place.naver.com/place/1101731614</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>팀키스짐 &amp; PT</t>
+          <t>VIP FITNESS 세경점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>teamkis_@naver.com</t>
+          <t>jaesoung12345@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1399-2305</t>
+          <t>033-742-0433</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 26 4층</t>
+          <t>강원특별자치도 원주시 단구로 424 세경웰러스상가 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamkis_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,24 +1062,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4olwd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,17 +1083,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2331</v>
+        <v>23</v>
       </c>
       <c r="Q7" t="n">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="R7" t="n">
-        <v>2834</v>
+        <v>106</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1433616376</t>
+          <t>1329264100</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433616376</t>
+          <t>https://m.place.naver.com/place/1329264100</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1152,25 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>크로스핏 컴뱃</t>
+          <t>바디라인휘트니스 원주무실점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>taiwansister@naver.com</t>
+          <t>bodyline2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1428-3415</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 만대공원길 64 1층</t>
+          <t>강원특별자치도 원주시 능라동길 48-1 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit__combat</t>
+          <t>https://blog.naver.com/bodyline2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1205,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>166</v>
+        <v>726</v>
       </c>
       <c r="Q8" t="n">
-        <v>44</v>
+        <v>733</v>
       </c>
       <c r="R8" t="n">
-        <v>210</v>
+        <v>1459</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,51 +1196,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36369149</t>
+          <t>1140023595</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36369149</t>
+          <t>https://m.place.naver.com/place/1140023595</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비브레 PT\u002F헬스 혁신점</t>
+          <t>리온 휘트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wonju_ht@naver.com</t>
+          <t>reon_fitness1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1354-8955</t>
+          <t>0507-1369-8925</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 건강로 17-2 6층 601~604호</t>
+          <t>강원특별자치도 원주시 문막읍 왕건로 81 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://vivre-training.com/</t>
+          <t>https://blog.naver.com/reon_fitness1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,19 +1255,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46eja</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>379</v>
+        <v>225</v>
       </c>
       <c r="Q9" t="n">
-        <v>2190</v>
+        <v>167</v>
       </c>
       <c r="R9" t="n">
-        <v>2569</v>
+        <v>392</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,51 +1290,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1193233179</t>
+          <t>1876515774</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193233179</t>
+          <t>https://m.place.naver.com/place/1876515774</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>목욕탕,사우나</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>하이컴뱃</t>
+          <t>청담사우나헬스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>taiwansister@naver.com</t>
+          <t>ohkfifa@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1347-5120</t>
+          <t>0507-1482-1126</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>강원 원주시 송삼길 19 1층</t>
+          <t>강원특별자치도 원주시 남원로534번길 64</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hycombat__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,7 +1344,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1393,17 +1365,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>322</v>
       </c>
       <c r="Q10" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="R10" t="n">
-        <v>37</v>
+        <v>351</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2058886633</t>
+          <t>1245074192</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2058886633</t>
+          <t>https://m.place.naver.com/place/1245074192</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1434,93 +1406,8795 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>비플로우PT&amp;그룹PT</t>
+          <t>TK바디브라운 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bflowpt@naver.com</t>
+          <t>cycnike201@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1437-1576</t>
+          <t>0507-1339-3020</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 9 3층 비플로우</t>
+          <t>강원특별자치도 원주시 능라동길 74 7층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/cycnike201</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>278</v>
+      </c>
+      <c r="R11" t="n">
+        <v>526</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1209497100</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1209497100</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>크로스핏BnK</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dldbsrnjs11@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1359-0221</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 나비허리길 97 2동 1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfitbnkyg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>198</v>
+      </c>
+      <c r="R12" t="n">
+        <v>221</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>37994071</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37994071</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>원포인트</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>onepointsoccer@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1338-1058</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 원문로 146 3층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>http://cfonepoint.itrocks.kr/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>653</v>
+      </c>
+      <c r="R13" t="n">
+        <v>662</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>36609953</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36609953</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ROAD GYM</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ghsk52@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>033-743-6766</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 시청로 80 쎈터프라자 10층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ghsk52</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>101</v>
+      </c>
+      <c r="R14" t="n">
+        <v>104</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>15247473</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15247473</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>훈짐 원주점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>hoongym@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>033-766-8221</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥업면 남원로 52-5 1층, 2층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hoongym</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>216</v>
+      </c>
+      <c r="R15" t="n">
+        <v>273</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1943954995</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1943954995</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>원주국제걷기대회</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>mmsus2392@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>kwf@walking.kr</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>033-762-2234</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 단구로 170 원주따뚜공연장</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>http://www.koreawalk.kr/</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>18</v>
+      </c>
+      <c r="R16" t="n">
+        <v>24</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13045168</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13045168</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>홍키통키 휘트니스 원주기업도시점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>hongkitongki-@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1413-9684</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 무릉로 35-1 3층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hongki_tongki_wonju</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>784</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>409</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1193</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1355839414</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1355839414</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>오디세이 피트니스</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>compuzonestory@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1320-7697</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 72 센트럴프라자2, 501호~504호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/odysseyfitness.kr/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2021582889</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2021582889</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>국제남여헬스클럽</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>hankyuldata@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>033-747-0993</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 평원초교길 2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>15223010</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15223010</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>24시 피트니스</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>24hourfitness_@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1313-4048</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 474 1, 2층 24시피트니스</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/24hoursfitness2020/?hl=ko</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>921</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>128</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1049</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1016379546</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1016379546</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>태장비타민휘트니스</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ugopower@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥양로18번길 33</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>32030333</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32030333</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>커브스 단구클럽</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>weonju007@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1447-4030</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 392 스타프라자 3층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/curvesdangu_</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>16</v>
+      </c>
+      <c r="R22" t="n">
+        <v>69</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>21547560</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21547560</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>비브레 PT/헬스 혁신점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>wonju_ht@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1354-8955</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 건강로 17-2 6층 601~604호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>http://vivre-training.com/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>381</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2190</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2571</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1193233179</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1193233179</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>펄핏 스튜디오 PT/헬스</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>gomete6363@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1389-9039</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 천매봉길 32-22 2층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pearl_fit_</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>124</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>368</v>
+      </c>
+      <c r="R24" t="n">
+        <v>492</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1471872878</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1471872878</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>원주인터불고 웰니스센터</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>yjw5443@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>033-769-8201</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 동부순환로 200</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>12</v>
+      </c>
+      <c r="R25" t="n">
+        <v>83</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1339846931</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1339846931</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HM 휘트니스</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>hm_7777@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1392-5874</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 396 2층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hm_7777</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>119</v>
+      </c>
+      <c r="R26" t="n">
+        <v>216</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>51291896</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/51291896</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>블루짐</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>bluegym_2412@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1443-7200</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 백간길 55 101-4호</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bluegym_2412</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1335716320</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1335716320</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>저스트포짐</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>24hourfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1472-1476</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 황금로 20 404호 저스트포짐</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/13/bizes/1409591</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>182</v>
+      </c>
+      <c r="R28" t="n">
+        <v>209</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1943100672</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1943100672</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>에이스스포츠센터&amp;에이스짐PT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jth3824@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1336-5769</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 원일로115번길 16 4층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/acegym_wonju</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>1587</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>919</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2506</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>15201329</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15201329</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>점핑스피닝GX</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>bata3012@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>033-813-0051</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 반곡초교로 77-2</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>11</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1972135147</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1972135147</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>헬스붐</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>wkdwnel4@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>033-734-9061</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥양로51번길 108</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>18</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>15282839</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15282839</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>올라운더짐 헬스&amp;PT 무실점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>allrounder_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1359-5382</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 솔우물2길 29-1 3층 올라운더 짐</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/allrounder_gym</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>47</v>
+      </c>
+      <c r="R32" t="n">
+        <v>104</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1497992346</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1497992346</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>해피짐 헬스&amp;PT 원주혁신점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0226juj@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1336-7769</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 봉황2길 17 3층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/happygym_official/</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>97</v>
+      </c>
+      <c r="R33" t="n">
+        <v>156</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2041898786</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2041898786</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>메가짐 PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>megagym9932@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1325-9932</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 165-3 아트스페이스 5층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/megagym9932</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>1735</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>338</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2073</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1302676152</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1302676152</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>상아휘트니스</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ablegym9@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>033-747-6398</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 바우골길 8 프렌티어스빌딩5층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>24</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>15214867</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15214867</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>코어척추운동센터</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>kbk9901016@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>070-7075-7544</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 만대로 148</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>http://cafe.daum.net/corebodygym0st</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>30820562</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/30820562</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>하디웨이트짐</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>hardyweightgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1334-8501</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 천사로 178 지하1층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hardyweightgym</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2034880654</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2034880654</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>크로스핏 컴뱃</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>taiwansister@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 만대공원길 64 1층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfit__combat</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>44</v>
+      </c>
+      <c r="R38" t="n">
+        <v>210</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>36369149</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36369149</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>스카이짐</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>seee9518@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>033-746-6080</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 남산로 180 8층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/seee9518</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>9</v>
+      </c>
+      <c r="R39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1340553997</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1340553997</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>유진헬스클럽</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>everfresh60@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>033-761-5959</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 황소마을길 40</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>5</v>
+      </c>
+      <c r="R40" t="n">
+        <v>19</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>11679515</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11679515</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>고고짐단구점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>histrionics92934@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1442-2113</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 늘품로 6 4층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>27</v>
+      </c>
+      <c r="R41" t="n">
+        <v>41</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1498521321</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1498521321</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>엔터핏헬스&amp;골프</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>enterfit_wonju@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1424-8254</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 입춘로 69 4층 401호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/enterfit_wonju/223823197126</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>279</v>
+      </c>
+      <c r="R42" t="n">
+        <v>335</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1866503944</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1866503944</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>호크아이짐 헬스/PT/태닝</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>hawkeyegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1307-5822</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 106 3층 호크아이짐</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hawkeyegym</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>4226</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>816</v>
+      </c>
+      <c r="R43" t="n">
+        <v>5042</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1602901180</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1602901180</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>무실동 듀플릿 헬스/PT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jin10240107@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1306-6059</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 70 5층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jin10240107</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>3511</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>742</v>
+      </c>
+      <c r="R44" t="n">
+        <v>4253</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1659772512</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1659772512</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>엠투짐</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>k1140391@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1358-1467</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 39-2 서울메디컬센터 5층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/m2gym.spinning</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>28</v>
+      </c>
+      <c r="R45" t="n">
+        <v>207</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>37912788</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37912788</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>블랑꼬 PT&amp;헬스 기업도시점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>dlarhkddbf1@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 신지정로 316-1 4층(골드파크빌딩)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dlarhkddbf1</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>270</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>166</v>
+      </c>
+      <c r="R46" t="n">
+        <v>436</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1401069241</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1401069241</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>하이컴뱃</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>taiwansister@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1347-5120</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 송삼길 19 1층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hycombat__</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>32</v>
+      </c>
+      <c r="R47" t="n">
+        <v>37</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>2058886633</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2058886633</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>크로스핏BK 혁신점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>thlqhd00@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1439-2177</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 웅비2길 10 봉우빌딩 B1층 크로스핏BK</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thlqhd00</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>124</v>
+      </c>
+      <c r="R48" t="n">
+        <v>179</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1074040282</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1074040282</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>비타민헬스클럽</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>shichichi@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>033-746-7494</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥양로18번길 33</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>16</v>
+      </c>
+      <c r="R49" t="n">
+        <v>77</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>15282842</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15282842</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>문막HM휘트니스</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>hm_7777@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1397-5874</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 문막읍 원문로 1595 2층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hm_7777</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>13</v>
+      </c>
+      <c r="R50" t="n">
+        <v>68</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1023016392</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1023016392</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>몬스터짐 요가&amp;PT헬스</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>chlwlgns6138@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1474-3328</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 건강로 23 4층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/chlwlgns6138</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>10</v>
+      </c>
+      <c r="R51" t="n">
+        <v>15</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2041484449</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2041484449</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>로드짐</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>moolbar@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>033-744-2626</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 37-2 5층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/moolbar</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>38</v>
+      </c>
+      <c r="R52" t="n">
+        <v>42</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1538542519</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1538542519</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>이룸바디스튜디오</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ghghgh2440@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1412-2449</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 백간길 55 2층 이룸바디스튜디오</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sYsj3q3c</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>40</v>
+      </c>
+      <c r="R53" t="n">
+        <v>107</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1611359768</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1611359768</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>제이엠피트니스</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>deny7004@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>033-733-3336</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 건강로 17 스타타워2. 5층 502호 503호 504호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/deny7004</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>15</v>
+      </c>
+      <c r="R54" t="n">
+        <v>48</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2005941753</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2005941753</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>히든헬스클럽</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>jayttt@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>033-762-1120</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 무실로 189 2층</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jayttt</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>100</v>
+      </c>
+      <c r="R55" t="n">
+        <v>124</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>38278726</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38278726</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>크로스핏에임 혁신점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>tafjq1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1319-5745</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 39-2 1층 107호, 108호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>7</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1853505932</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853505932</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>반곡뮤직스피닝</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>zkscy293@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1335-4279</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 늘품로 187-58 현대아카데미 5층 뮤직스피닝</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/musicspinning_bangok?igsh=MW55NGxzaHFrZG4yZw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>21</v>
+      </c>
+      <c r="R57" t="n">
+        <v>64</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1766314585</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1766314585</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>블랑꼬 PT&amp;헬스 태장점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>dlarhkddbf1@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1330-4023</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥양로18번길 35 . 지하 1층&amp;2층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dlarhkddbf1</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>59</v>
+      </c>
+      <c r="R58" t="n">
+        <v>144</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1901538636</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1901538636</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Confidence GYM</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>confidencegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 남원로534번길 51</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>2</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1411151781</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1411151781</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>팀키스짐 &amp; PT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>teamkis_@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1399-2305</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 26 4층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teamkis_</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>2331</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>504</v>
+      </c>
+      <c r="R60" t="n">
+        <v>2835</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1433616376</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1433616376</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>엑스스피닝</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>spinning1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1361-2234</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 51 시네시티타워 6층 619호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spinning1004</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>38</v>
+      </c>
+      <c r="R61" t="n">
+        <v>61</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1195598010</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1195598010</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>대동헬스피아</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>onsi09@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>033-748-3279</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 북원상가길 13 북원상가 3층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://ok114.co.kr/0337483279</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>6</v>
+      </c>
+      <c r="R62" t="n">
+        <v>12</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>15282840</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15282840</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>비타민헬스</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>chima7988@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>033-732-8210</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 행구로 79</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2</v>
+      </c>
+      <c r="R63" t="n">
+        <v>10</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>34050723</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34050723</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>더바른PT / 헬스 혁신점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>thebarnnpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1491-1113</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 53 4층 더바른PT</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/thebarnnpt</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>243</v>
+      </c>
+      <c r="R64" t="n">
+        <v>422</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1850025502</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850025502</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>아이두 PT&amp;그룹PT</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>foreverido9993@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1425-0383</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 51 819호,820호,821호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/foreverido9993</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>43</v>
+      </c>
+      <c r="R65" t="n">
+        <v>157</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1973853263</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1973853263</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>더에스짐</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>thesgym3736@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1442-0884</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 영랑길 13 그린빌딩 7층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2043004666</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2043004666</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>스웻버디 PT스튜디오</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>pttrainiggym@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1318-3448</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 바우골길 22-4 1층 포스빌</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pttrainiggym</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>10</v>
+      </c>
+      <c r="R67" t="n">
+        <v>14</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1800206345</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1800206345</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>네츄럴 올림피아</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ojg4205@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>033-732-0035</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 시청로 160-1 노블인갤러리 2F (법원맞은편)</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>31674353</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31674353</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>비플로우PT&amp;그룹PT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>bflowpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1437-1576</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 9 3층 비플로우</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>https://blog.naver.com/bflowpt</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h9q7</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
         <v>235</v>
       </c>
-      <c r="Q11" t="n">
-        <v>665</v>
-      </c>
-      <c r="R11" t="n">
-        <v>900</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="Q69" t="n">
+        <v>666</v>
+      </c>
+      <c r="R69" t="n">
+        <v>901</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
         <is>
           <t>1870827414</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1870827414</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>컨피던스짐 단구점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>confidencegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1348-9679</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 남원로534번길 51 2층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/confidence_1st</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>321</v>
+      </c>
+      <c r="R70" t="n">
+        <v>441</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1250040920</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1250040920</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>몸수선토탈케어PT샵</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>dmsal04@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1423-0830</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 천매봉길 58 1층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/momsuseon?igsh=d3NiM3MwNTYzaXA4</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>37</v>
+      </c>
+      <c r="R71" t="n">
+        <v>37</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1964597317</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1964597317</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>바디스튜디오카모</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>note3737@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1334-9997</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 로아노크로 28 402호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="n">
+        <v>2</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1515432168</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1515432168</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>컨피던스짐 원주 단계점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>confidencegym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1444-9680</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 단구로 80 1층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>29</v>
+      </c>
+      <c r="R73" t="n">
+        <v>53</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1341284821</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1341284821</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>혁신런앤핏</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>hghghghg00@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1346-7262</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 19 지하층 101호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hs_run_fit</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>23</v>
+      </c>
+      <c r="R74" t="n">
+        <v>23</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1223719800</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1223719800</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>헤이스바디랩</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>heisbodylab@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0506-571-3069</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥양로51번길 1 원마트 2층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/heis_body_lab</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>205</v>
+      </c>
+      <c r="R75" t="n">
+        <v>211</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1399142746</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1399142746</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>바디아카데미 PT 프리미엄센터</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>dlrlckdtkdwl@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>033-900-7450</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 34-1 센트럴프라자 3차 3층 바디아카데미 PT 프리미엄센터</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ki_chang_l/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>594</v>
+      </c>
+      <c r="R76" t="n">
+        <v>681</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1329553206</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1329553206</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>노익스짐 PT</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>no_x_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1486-6692</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 무실본동길 38 1층 노익스짐</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/no_x_gym</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>289</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>864</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1153</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1213015794</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213015794</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>리햅포먼스</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>rehabformance@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1324-4662</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 만대로 166 4층 리햅포먼스</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rehabformance</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>71</v>
+      </c>
+      <c r="R78" t="n">
+        <v>131</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1229524729</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1229524729</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>건강해GYM</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>sjoon0614@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1315-5985</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 백간공원길 29 2층 건강해GYM</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sjoon0614</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>4</v>
+      </c>
+      <c r="R79" t="n">
+        <v>4</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1326301902</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1326301902</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>조거앤스웨트</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>woonduong@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1447-9913</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 혁신로 35 202호</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jogger_sweat</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>16</v>
+      </c>
+      <c r="R80" t="n">
+        <v>28</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1412402393</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1412402393</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>더피티라운지</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>the_pt_lounge@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1327-2648</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 버들만이길 3-1 1층</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_mbYxbb</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>42</v>
+      </c>
+      <c r="R81" t="n">
+        <v>129</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1798078297</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1798078297</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>다르짐</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>lozebons@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1358-9021</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 섬밭들1길 26-9 1층 다르짐</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/runner_dar/</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1344578636</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1344578636</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>율핏피트니스 PT센터 무실점</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>yulgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 65 휴먼타워 9층 902호 903호 (무실동 1857-1)</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yulgym</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>486</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>522</v>
+      </c>
+      <c r="R83" t="n">
+        <v>1008</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>481098140</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/481098140</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>OK시니어체인지클럽</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>okscc-@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1481-0006</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 402 4층 402호</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://연세오케이정형외과.kr/ok-change-club</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>77</v>
+      </c>
+      <c r="R84" t="n">
+        <v>88</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>2086283255</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2086283255</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>엑스바디 PT 스튜디오 무실동</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>xbody1101@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 시청로 86 부영골든빌 4층 403호</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/x.body_ptstudio</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>316</v>
+      </c>
+      <c r="R85" t="n">
+        <v>432</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1571856002</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1571856002</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>바디팩토리웰니스짐</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>rntjdah2@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 만대로 158</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rntjdah2</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>55</v>
+      </c>
+      <c r="R86" t="n">
+        <v>55</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>35958713</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35958713</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>핏앤피트니스 PT &amp; 그룹피티</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ssz1549@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1445-0383</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 47 8층,핏앤피트니스</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@hipupschool</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>778</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1016</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1793276177</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1793276177</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>바디아카데미 기업도시점</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>juseokchan91@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1393-4411</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 신지정로 212 롯데퍼스트프라자 6층 바디아카데미</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>151</v>
+      </c>
+      <c r="R88" t="n">
+        <v>157</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1896388555</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1896388555</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>다이아짐</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>top-health@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1428-5618</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 37 302호</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>3</v>
+      </c>
+      <c r="R89" t="n">
+        <v>3</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1877473254</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1877473254</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>터틀짐</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>turtlegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>070-7543-1528</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 남원로 528-31 신세계프라자 5층 터틀짐</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>7</v>
+      </c>
+      <c r="R90" t="n">
+        <v>15</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1249823565</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1249823565</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>핏앤피트니스 PT &amp; 그룹피티 기업점</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>rlghks405@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1328-0301</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 신지정로 172 6층</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlghks405</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>292</v>
+      </c>
+      <c r="R91" t="n">
+        <v>395</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1139721387</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1139721387</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>바디플렉스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>dlehfla1@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1393-5547</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 행구로 95 지하1층</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>5</v>
+      </c>
+      <c r="R92" t="n">
+        <v>89</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1791374940</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1791374940</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>비앤비 운동센터</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>sbsun486@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 북원로 2613 2층 206호</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>2</v>
+      </c>
+      <c r="R93" t="n">
+        <v>2</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1091075931</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1091075931</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>핏앤피트니스 혁신점</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ssb154911@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>033-735-0302</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 미래로 1 강림빌딩 3층 302호</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://fitandfitness.imweb.me</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>284</v>
+      </c>
+      <c r="R94" t="n">
+        <v>406</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1042681042</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1042681042</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>바디아카데미 혁신도시점</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>wkdgusxo12345@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1493-4412</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 양지로 20 오썸파크 209호</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/body___academy_ht</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>86</v>
+      </c>
+      <c r="R95" t="n">
+        <v>154</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1128838469</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1128838469</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>원주무실동프리미엄피티</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>yunsiin@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 로아노크로 76 1층</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>3</v>
+      </c>
+      <c r="R96" t="n">
+        <v>18</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1217507491</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1217507491</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>클래식짐 PT 혁신점</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>classicgym2749@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1313-2749</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 황금로 20 5층 502호</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/classicgym2749</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>84</v>
+      </c>
+      <c r="R97" t="n">
+        <v>160</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1324878145</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1324878145</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>본움 체형교정 선수트레이닝 센터</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>rlghks00235@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0507-1336-1466</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 미래로 1 3층 303호</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlghks00235</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>48</v>
+      </c>
+      <c r="R98" t="n">
+        <v>56</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>2088505203</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2088505203</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>실내체육관</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>원주남부 복합체육센터</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>wonju_city@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>033-737-4955</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 이화5길 70</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.wonju.go.kr/www/contents.do?key=6028&amp;</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>83</v>
+      </c>
+      <c r="R99" t="n">
+        <v>111</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>1282336869</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1282336869</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>실내체육관</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>원주시농민문화체육센터</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>033-737-4725</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 문막읍 건등로 21 농민문화체육센터</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://yeyak.wonju.go.kr/www/main.do</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>48</v>
+      </c>
+      <c r="R100" t="n">
+        <v>174</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>21387721</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21387721</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>실내체육관</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>원주드림체육관</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>anaber@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>033-737-4666</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 현충로 53-1 원주드림체육관</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://www.wonju.go.kr/facility/contents.do?key=6385&amp;</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>43</v>
+      </c>
+      <c r="R101" t="n">
+        <v>163</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>34605311</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34605311</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>요가,명상</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>지성요가원</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>wonju_jisung_yoga@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1401-0382</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 시청로 94 보네르 빌딩 4층 지성요가원</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jisung_yoga_wonju/</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>59</v>
+      </c>
+      <c r="R102" t="n">
+        <v>146</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>31992339</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31992339</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>찜질방</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>대성인터스파</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>bow_land@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>033-732-1006</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 남산로 180 대성빌딩 2-4층</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>23</v>
+      </c>
+      <c r="R103" t="n">
+        <v>259</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>11573515</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11573515</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>체육관</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>에임크로스핏</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>newtriple@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0507-1415-6004</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 북원로 1897 1층~2층</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/aim_crossfit</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>150</v>
+      </c>
+      <c r="R104" t="n">
+        <v>155</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>1062060537</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1062060537</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
